--- a/get_embedding/CGCNN_MEGNet.xlsx
+++ b/get_embedding/CGCNN_MEGNet.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22270" windowHeight="10480"/>
+    <workbookView windowWidth="15945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -844,7 +842,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,14 +862,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1399,21 +1395,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="21.8727272727273" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.875" style="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="2"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
-    <col min="5" max="7" width="10.3727272727273" style="3"/>
-    <col min="8" max="8" width="10.2818181818182" style="3" customWidth="1"/>
+    <col min="5" max="7" width="10.375" style="3"/>
+    <col min="8" max="8" width="10.2833333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="10.4363636363636" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.95454545454546" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.2909090909091" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.3181818181818" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.6181818181818" style="3" customWidth="1"/>
-    <col min="15" max="15" width="10.4363636363636" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.4636363636364" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.4333333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.95833333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.2916666666667" style="3" customWidth="1"/>
+    <col min="13" max="13" width="11.3166666666667" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.6166666666667" style="3" customWidth="1"/>
+    <col min="15" max="15" width="10.4333333333333" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.4666666666667" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -1474,46 +1470,46 @@
       <c r="B2" s="6">
         <v>34.6264</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>47.509</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>40.277412</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>39.522293</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>38.027626</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>37.377113</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>38.510025</v>
       </c>
       <c r="I2" s="4">
         <v>8</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>35.5468</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>39.0077</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="9">
         <v>35.486977</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="9">
         <v>34.732582</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="9">
         <v>35.088345</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="9">
         <v>33.75198</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>33.221779</v>
       </c>
     </row>
@@ -1521,22 +1517,22 @@
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>49.55</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>60.282</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>61.100941</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>61.110989</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>60.14365</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>61.415848</v>
       </c>
       <c r="H3" s="6">
@@ -1548,22 +1544,22 @@
       <c r="J3" s="6">
         <v>53.6503</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>58.7821</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>65.741821</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>61.14204</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>55.493393</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>54.680233</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="9">
         <v>54.8367</v>
       </c>
     </row>
@@ -1574,46 +1570,46 @@
       <c r="B4" s="6">
         <v>70.818</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>76.2431</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>78.244064</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>77.89476</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>77.040192</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>76.685936</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>91.610039</v>
       </c>
       <c r="I4" s="4">
         <v>8</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>72.9783</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>78.1044</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>82.793915</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>73.663269</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="9">
         <v>69.370155</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>74.724617</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="9">
         <v>74.77739</v>
       </c>
     </row>
@@ -1621,49 +1617,49 @@
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>45.9535</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>43.1261</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>56.406269</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>43.611374</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>45.757572</v>
       </c>
       <c r="G5" s="6">
         <v>36.163273</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>45.581623</v>
       </c>
       <c r="I5" s="4">
         <v>8</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>45.4462</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <v>44.9232</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>45.171558</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="9">
         <v>43.865917</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="9">
         <v>37.723232</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="9">
         <v>35.299232</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="9">
         <v>46.256241</v>
       </c>
     </row>
@@ -1671,49 +1667,49 @@
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>51.9283</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>56.8497</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>54.047253</v>
       </c>
       <c r="E6" s="6">
         <v>48.834454</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>55.327557</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>49.319744</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>52.868126</v>
       </c>
       <c r="I6" s="4">
         <v>8</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>51.418</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>52.3787</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>52.118221</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>52.349983</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <v>55.096786</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="9">
         <v>51.76511</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="9">
         <v>51.201504</v>
       </c>
     </row>
@@ -1721,49 +1717,49 @@
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>40.5406</v>
       </c>
       <c r="C7" s="6">
         <v>33.8014</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>39.41293</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>37.536087</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>45.158318</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>40.071686</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>33.871132</v>
       </c>
       <c r="I7" s="4">
         <v>16</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>36.6016</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>39.7227</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>38.742718</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="9">
         <v>36.054611</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="9">
         <v>36.197845</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="9">
         <v>38.071045</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="9">
         <v>38.491764</v>
       </c>
     </row>
@@ -1771,22 +1767,22 @@
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>51.972</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>60.4277</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>59.507183</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>60.593002</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>67.628372</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>55.843956</v>
       </c>
       <c r="H8" s="6">
@@ -1798,22 +1794,22 @@
       <c r="J8" s="6">
         <v>53.8173</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <v>57.5576</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>60.323074</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <v>58.241474</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <v>57.943398</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="9">
         <v>55.383442</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="9">
         <v>55.562805</v>
       </c>
     </row>
@@ -1821,10 +1817,10 @@
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>72.8043</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>75.6955</v>
       </c>
       <c r="D9" s="6">
@@ -1833,13 +1829,13 @@
       <c r="E9" s="6">
         <v>72.543633</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>81.100624</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>78.08403</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>75.864296</v>
       </c>
       <c r="I9" s="4">
@@ -1848,22 +1844,22 @@
       <c r="J9" s="6">
         <v>70.5222</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <v>76.4589</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>77.777489</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <v>83.063896</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <v>73.109993</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="9">
         <v>75.359344</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="9">
         <v>73.254318</v>
       </c>
     </row>
@@ -1871,22 +1867,22 @@
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>43.3224</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>40.5564</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>44.907112</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>41.859966</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>41.492958</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>41.48354</v>
       </c>
       <c r="H10" s="6">
@@ -1895,25 +1891,25 @@
       <c r="I10" s="4">
         <v>16</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>37.4998</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <v>48.4632</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>43.561268</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <v>42.237537</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <v>40.726326</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="9">
         <v>32.320065</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="9">
         <v>35.516884</v>
       </c>
     </row>
@@ -1921,22 +1917,22 @@
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>54.8633</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>55.6181</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>51.292366</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>72.219742</v>
       </c>
       <c r="F11" s="6">
         <v>54.509632</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>56.167843</v>
       </c>
       <c r="H11" s="6">
@@ -1945,25 +1941,25 @@
       <c r="I11" s="4">
         <v>16</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>54.8218</v>
       </c>
       <c r="K11" s="6">
         <v>52.3132</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <v>53.927856</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="9">
         <v>56.605831</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="9">
         <v>54.962334</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="9">
         <v>54.483437</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="9">
         <v>54.594635</v>
       </c>
     </row>
@@ -1971,19 +1967,19 @@
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>37.7047</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>35.5464</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>43.703144</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>39.628574</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>38.52182</v>
       </c>
       <c r="G12" s="6">
@@ -1998,22 +1994,22 @@
       <c r="J12" s="6">
         <v>34.2904</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <v>35.9229</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="9">
         <v>41.478149</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="9">
         <v>35.750687</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="9">
         <v>45.577461</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="9">
         <v>34.332314</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="9">
         <v>35.718613</v>
       </c>
     </row>
@@ -2021,22 +2017,22 @@
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>54.5983</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>60.7463</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>70.668251</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>65.833015</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>69.164299</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>56.589428</v>
       </c>
       <c r="H13" s="6">
@@ -2045,25 +2041,25 @@
       <c r="I13" s="4">
         <v>32</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>58.9461</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <v>57.2207</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="9">
         <v>59.347172</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="9">
         <v>56.731522</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="9">
         <v>57.520195</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="9">
         <v>57.438347</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="9">
         <v>53.689571</v>
       </c>
     </row>
@@ -2071,25 +2067,25 @@
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>74.5022</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>74.0952</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>76.796341</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>79.188263</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>78.693497</v>
       </c>
       <c r="G14" s="6">
         <v>70.864822</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>75.448685</v>
       </c>
       <c r="I14" s="4">
@@ -2098,22 +2094,22 @@
       <c r="J14" s="6">
         <v>72.6142</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <v>77.2137</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>85.824051</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <v>79.293282</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>74.334938</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>74.576385</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="9">
         <v>75.549751</v>
       </c>
     </row>
@@ -2121,49 +2117,49 @@
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>38.7505</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>45.1965</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>44.727161</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>46.307285</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>42.759056</v>
       </c>
       <c r="G15" s="6">
         <v>38.27869</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>40.17485</v>
       </c>
       <c r="I15" s="4">
         <v>32</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="6">
         <v>33.9942</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="6">
         <v>40.1483</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="9">
         <v>41.759701</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="9">
         <v>41.625423</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="9">
         <v>39.300053</v>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="9">
         <v>33.952904</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="9">
         <v>34.173576</v>
       </c>
     </row>
@@ -2171,22 +2167,22 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>52.9093</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>54.8211</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>66.138153</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>60.40662</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>68.66555</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="6">
         <v>54.164307</v>
       </c>
       <c r="H16" s="6">
@@ -2195,25 +2191,25 @@
       <c r="I16" s="4">
         <v>32</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="6">
         <v>53.3324</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="6">
         <v>54.2649</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="9">
         <v>53.382042</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="9">
         <v>53.636555</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <v>53.728989</v>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="9">
         <v>50.16901</v>
       </c>
-      <c r="P16" s="11">
+      <c r="P16" s="9">
         <v>48.803806</v>
       </c>
     </row>
@@ -2221,19 +2217,19 @@
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>33.9252</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>39.9988</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>39.050831</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>39.136257</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>38.868473</v>
       </c>
       <c r="G17" s="6">
@@ -2245,25 +2241,25 @@
       <c r="I17" s="4">
         <v>64</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="6">
         <v>35.8297</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="6">
         <v>40.7079</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>39.573582</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>37.648056</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>39.393078</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="9">
         <v>35.070938</v>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="9">
         <v>34.856243</v>
       </c>
     </row>
@@ -2271,22 +2267,22 @@
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>52.0475</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>59.2876</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>59.989975</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>60.066402</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>68.945999</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>59.721329</v>
       </c>
       <c r="H18" s="6">
@@ -2295,25 +2291,25 @@
       <c r="I18" s="4">
         <v>64</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="6">
         <v>55.7533</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="6">
         <v>55.5228</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>55.799648</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>56.26474</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>55.717026</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="9">
         <v>54.592728</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="9">
         <v>59.437668</v>
       </c>
     </row>
@@ -2321,25 +2317,25 @@
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>72.4178</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>73.4527</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>77.336166</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>77.305649</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>76.381424</v>
       </c>
       <c r="G19" s="6">
         <v>72.020203</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>72.973007</v>
       </c>
       <c r="I19" s="4">
@@ -2348,22 +2344,22 @@
       <c r="J19" s="6">
         <v>71.8743</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>77.8357</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>77.640709</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>79.935905</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="9">
         <v>83.189819</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="9">
         <v>73.229439</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="9">
         <v>74.160141</v>
       </c>
     </row>
@@ -2371,49 +2367,49 @@
       <c r="A20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>38.3032</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>45.7843</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>43.13538</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>43.10281</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>40.864822</v>
       </c>
       <c r="G20" s="6">
         <v>37.644127</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>43.40694</v>
       </c>
       <c r="I20" s="4">
         <v>64</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="6">
         <v>37.8869</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="6">
         <v>40.8487</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>42.618412</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="9">
         <v>42.488575</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>44.031036</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="9">
         <v>41.129913</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="9">
         <v>34.814285</v>
       </c>
     </row>
@@ -2421,19 +2417,19 @@
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>58.4058</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>60.1287</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="6">
         <v>60.421703</v>
       </c>
       <c r="E21" s="6">
         <v>57.969372</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>58.892368</v>
       </c>
       <c r="G21" s="6">
@@ -2445,84 +2441,84 @@
       <c r="I21" s="4">
         <v>64</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="6">
         <v>52.1467</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="6">
         <v>52.9925</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>54.225639</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="9">
         <v>50.98991</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="9">
         <v>51.78434</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="9">
         <v>53.239037</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="9">
         <v>54.856823</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="8"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>69.1774</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>120.856</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>96.274506</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6">
         <v>95.946136</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>94.26059</v>
       </c>
       <c r="G23" s="6">
         <v>68.366882</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <v>72.201866</v>
       </c>
       <c r="I23" s="4">
         <v>8</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="6">
         <v>37.1543</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="6">
         <v>35.2972</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="6">
         <v>46.642941</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="6">
         <v>39.119461</v>
       </c>
       <c r="N23" s="6">
@@ -2531,7 +2527,7 @@
       <c r="O23" s="6">
         <v>32.283886</v>
       </c>
-      <c r="P23" s="7">
+      <c r="P23" s="6">
         <v>36.243649</v>
       </c>
     </row>
@@ -2539,10 +2535,10 @@
       <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>86.7573</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>95.0136</v>
       </c>
       <c r="D24" s="6">
@@ -2563,22 +2559,22 @@
       <c r="I24" s="4">
         <v>8</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="6">
         <v>31.5678</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="6">
         <v>35.1948</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="6">
         <v>33.544285</v>
       </c>
       <c r="M24" s="6">
         <v>31.44475</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="6">
         <v>34.272106</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="6">
         <v>32.625092</v>
       </c>
       <c r="P24" s="6">
@@ -2589,16 +2585,16 @@
       <c r="A25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>92.1144</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>107.588</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>95.771378</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6">
         <v>93.460251</v>
       </c>
       <c r="F25" s="6">
@@ -2613,25 +2609,25 @@
       <c r="I25" s="4">
         <v>8</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="6">
         <v>31.6719</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="6">
         <v>34.8631</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="6">
         <v>37.003403</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="6">
         <v>34.919949</v>
       </c>
       <c r="N25" s="6">
         <v>30.718414</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="6">
         <v>34.281818</v>
       </c>
-      <c r="P25" s="7">
+      <c r="P25" s="6">
         <v>35.08593</v>
       </c>
     </row>
@@ -2639,19 +2635,19 @@
       <c r="A26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>76.3721</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>106.322</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>84.717636</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="6">
         <v>86.915909</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>87.942932</v>
       </c>
       <c r="G26" s="6">
@@ -2663,25 +2659,25 @@
       <c r="I26" s="4">
         <v>8</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="6">
         <v>31.1402</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="6">
         <v>34.5559</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="6">
         <v>35.54425</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="6">
         <v>37.353241</v>
       </c>
       <c r="N26" s="6">
         <v>28.258627</v>
       </c>
-      <c r="O26" s="7">
+      <c r="O26" s="6">
         <v>34.396431</v>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="6">
         <v>32.551662</v>
       </c>
     </row>
@@ -2689,22 +2685,22 @@
       <c r="A27" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>66.2471</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>83.6487</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>104.484222</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <v>89.597626</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>84.891022</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <v>68.676422</v>
       </c>
       <c r="H27" s="6">
@@ -2716,22 +2712,22 @@
       <c r="J27" s="6">
         <v>27.5564</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <v>32.9901</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="6">
         <v>33.289295</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <v>34.064358</v>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="6">
         <v>31.237625</v>
       </c>
-      <c r="O27" s="7">
+      <c r="O27" s="6">
         <v>31.019867</v>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="6">
         <v>31.477057</v>
       </c>
     </row>
@@ -2742,46 +2738,46 @@
       <c r="B28" s="6">
         <v>69.7537</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>130.563</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>118.474365</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="6">
         <v>118.30632</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <v>119.276619</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="6">
         <v>89.178764</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>91.112305</v>
       </c>
       <c r="I28" s="4">
         <v>16</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="6">
         <v>36.1342</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="6">
         <v>34.5324</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="6">
         <v>36.271835</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="6">
         <v>39.164181</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="6">
         <v>41.591999</v>
       </c>
       <c r="O28" s="6">
         <v>33.853916</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="6">
         <v>37.190636</v>
       </c>
     </row>
@@ -2792,31 +2788,31 @@
       <c r="B29" s="6">
         <v>58.9779</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="6">
         <v>74.4017</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>76.018448</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="6">
         <v>74.359055</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="6">
         <v>89.372971</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="6">
         <v>76.500366</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>61.439396</v>
       </c>
       <c r="I29" s="4">
         <v>16</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="6">
         <v>34.0485</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="6">
         <v>33.923</v>
       </c>
       <c r="L29" s="6">
@@ -2839,22 +2835,22 @@
       <c r="A30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>75.1454</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="6">
         <v>99.0716</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>108.110443</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="6">
         <v>115.398575</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <v>91.568604</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="6">
         <v>81.624626</v>
       </c>
       <c r="H30" s="6">
@@ -2863,25 +2859,25 @@
       <c r="I30" s="4">
         <v>16</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="6">
         <v>31.2317</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="6">
         <v>33.611</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="6">
         <v>33.45636</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="6">
         <v>34.970997</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N30" s="6">
         <v>33.707363</v>
       </c>
       <c r="O30" s="6">
         <v>30.670359</v>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="6">
         <v>54.842377</v>
       </c>
     </row>
@@ -2892,46 +2888,46 @@
       <c r="B31" s="6">
         <v>58.6123</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="6">
         <v>89.3951</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>92.184799</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="6">
         <v>94.961624</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <v>108.008423</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="6">
         <v>59.447617</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="6">
         <v>64.624115</v>
       </c>
       <c r="I31" s="4">
         <v>16</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="6">
         <v>31.0156</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="6">
         <v>32.7851</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L31" s="6">
         <v>33.907871</v>
       </c>
       <c r="M31" s="6">
         <v>30.731129</v>
       </c>
-      <c r="N31" s="7">
+      <c r="N31" s="6">
         <v>34.162556</v>
       </c>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <v>31.377764</v>
       </c>
-      <c r="P31" s="7">
+      <c r="P31" s="6">
         <v>37.21669</v>
       </c>
     </row>
@@ -2939,49 +2935,49 @@
       <c r="A32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>70.8958</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>97.2643</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>90.303757</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="6">
         <v>104.77224</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <v>117.820465</v>
       </c>
       <c r="G32" s="6">
         <v>67.740433</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="6">
         <v>72.95018</v>
       </c>
       <c r="I32" s="4">
         <v>16</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="6">
         <v>28.6839</v>
       </c>
       <c r="K32" s="6">
         <v>27.99</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="6">
         <v>30.839666</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="6">
         <v>28.818125</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="6">
         <v>34.619255</v>
       </c>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <v>30.380461</v>
       </c>
-      <c r="P32" s="7">
+      <c r="P32" s="6">
         <v>29.728704</v>
       </c>
     </row>
@@ -2989,22 +2985,22 @@
       <c r="A33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="6">
         <v>87.2947</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="6">
         <v>128.814</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="6">
         <v>125.256714</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="6">
         <v>125.243408</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <v>118.752914</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="6">
         <v>88.242584</v>
       </c>
       <c r="H33" s="6">
@@ -3013,10 +3009,10 @@
       <c r="I33" s="4">
         <v>32</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="6">
         <v>36.347</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="6">
         <v>37.9691</v>
       </c>
       <c r="L33" s="6">
@@ -3025,13 +3021,13 @@
       <c r="M33" s="6">
         <v>33.515869</v>
       </c>
-      <c r="N33" s="7">
+      <c r="N33" s="6">
         <v>38.269131</v>
       </c>
       <c r="O33" s="6">
         <v>34.393475</v>
       </c>
-      <c r="P33" s="7">
+      <c r="P33" s="6">
         <v>132.30336</v>
       </c>
     </row>
@@ -3039,19 +3035,19 @@
       <c r="A34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="6">
         <v>64.3254</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <v>83.5193</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>76.839943</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="6">
         <v>76.857864</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <v>73.703049</v>
       </c>
       <c r="G34" s="6">
@@ -3063,10 +3059,10 @@
       <c r="I34" s="4">
         <v>32</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="6">
         <v>33.764</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="6">
         <v>36.4725</v>
       </c>
       <c r="L34" s="6">
@@ -3089,22 +3085,22 @@
       <c r="A35" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>72.4148</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>106.954</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>117.042717</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>117.047318</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <v>101.980759</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="6">
         <v>74.915741</v>
       </c>
       <c r="H35" s="6">
@@ -3113,10 +3109,10 @@
       <c r="I35" s="4">
         <v>32</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="6">
         <v>35.5088</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="6">
         <v>33.8133</v>
       </c>
       <c r="L35" s="6">
@@ -3128,10 +3124,10 @@
       <c r="N35" s="6">
         <v>33.309273</v>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>35.339916</v>
       </c>
-      <c r="P35" s="7">
+      <c r="P35" s="6">
         <v>35.971199</v>
       </c>
     </row>
@@ -3139,40 +3135,40 @@
       <c r="A36" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="6">
         <v>59.6454</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>99.4637</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>87.695686</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="6">
         <v>87.637375</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <v>84.441391</v>
       </c>
       <c r="G36" s="6">
         <v>57.96183</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="6">
         <v>63.427925</v>
       </c>
       <c r="I36" s="4">
         <v>32</v>
       </c>
-      <c r="J36" s="7">
+      <c r="J36" s="6">
         <v>33.1695</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="6">
         <v>33.9819</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="6">
         <v>38.313744</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="6">
         <v>35.002892</v>
       </c>
       <c r="N36" s="6">
@@ -3192,43 +3188,43 @@
       <c r="B37" s="6">
         <v>62.8167</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>101.671</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>89.15715</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="6">
         <v>89.231026</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="6">
         <v>102.139679</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="6">
         <v>69.256821</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="6">
         <v>70.966652</v>
       </c>
       <c r="I37" s="4">
         <v>32</v>
       </c>
-      <c r="J37" s="7">
+      <c r="J37" s="6">
         <v>31.9893</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K37" s="6">
         <v>28.4422</v>
       </c>
-      <c r="L37" s="7">
+      <c r="L37" s="6">
         <v>29.13669</v>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="6">
         <v>31.102736</v>
       </c>
-      <c r="N37" s="7">
+      <c r="N37" s="6">
         <v>28.55312</v>
       </c>
-      <c r="O37" s="7">
+      <c r="O37" s="6">
         <v>30.552324</v>
       </c>
       <c r="P37" s="6">
@@ -3239,19 +3235,19 @@
       <c r="A38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <v>97.846</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="6">
         <v>119.008</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>129.49205</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="6">
         <v>129.524139</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <v>132.831284</v>
       </c>
       <c r="G38" s="6">
@@ -3263,19 +3259,19 @@
       <c r="I38" s="4">
         <v>64</v>
       </c>
-      <c r="J38" s="7">
+      <c r="J38" s="6">
         <v>36.2501</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K38" s="6">
         <v>40.2582</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="6">
         <v>38.967598</v>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="6">
         <v>48.078758</v>
       </c>
-      <c r="N38" s="7">
+      <c r="N38" s="6">
         <v>43.533016</v>
       </c>
       <c r="O38" s="6">
@@ -3289,25 +3285,25 @@
       <c r="A39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <v>64.8963</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="6">
         <v>81.0521</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>81.471481</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="6">
         <v>81.493408</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="6">
         <v>84.076187</v>
       </c>
       <c r="G39" s="6">
         <v>54.118931</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="6">
         <v>65.611908</v>
       </c>
       <c r="I39" s="4">
@@ -3316,22 +3312,22 @@
       <c r="J39" s="6">
         <v>32.4725</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="6">
         <v>37.7599</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="6">
         <v>66.860199</v>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="6">
         <v>32.88628</v>
       </c>
-      <c r="N39" s="7">
+      <c r="N39" s="6">
         <v>36.600296</v>
       </c>
-      <c r="O39" s="7">
+      <c r="O39" s="6">
         <v>32.978516</v>
       </c>
-      <c r="P39" s="7">
+      <c r="P39" s="6">
         <v>37.922977</v>
       </c>
     </row>
@@ -3339,49 +3335,49 @@
       <c r="A40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="6">
         <v>78.0186</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="6">
         <v>103.318</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>98.131332</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="6">
         <v>98.130661</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="6">
         <v>102.783684</v>
       </c>
       <c r="G40" s="6">
         <v>66.031029</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="6">
         <v>85.245651</v>
       </c>
       <c r="I40" s="4">
         <v>64</v>
       </c>
-      <c r="J40" s="7">
+      <c r="J40" s="6">
         <v>34.9728</v>
       </c>
       <c r="K40" s="6">
         <v>31.928</v>
       </c>
-      <c r="L40" s="7">
+      <c r="L40" s="6">
         <v>37.516808</v>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="6">
         <v>43.494225</v>
       </c>
-      <c r="N40" s="7">
+      <c r="N40" s="6">
         <v>58.859531</v>
       </c>
-      <c r="O40" s="7">
+      <c r="O40" s="6">
         <v>34.519985</v>
       </c>
-      <c r="P40" s="7">
+      <c r="P40" s="6">
         <v>40.282993</v>
       </c>
     </row>
@@ -3389,25 +3385,25 @@
       <c r="A41" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="6">
         <v>63.443</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="6">
         <v>80.6628</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>87.866783</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="6">
         <v>87.86866</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="6">
         <v>90.718018</v>
       </c>
       <c r="G41" s="6">
         <v>58.342033</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="6">
         <v>65.367126</v>
       </c>
       <c r="I41" s="4">
@@ -3416,22 +3412,22 @@
       <c r="J41" s="6">
         <v>33.334</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="6">
         <v>34.3438</v>
       </c>
-      <c r="L41" s="7">
+      <c r="L41" s="6">
         <v>50.893326</v>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="6">
         <v>50.695705</v>
       </c>
-      <c r="N41" s="7">
+      <c r="N41" s="6">
         <v>46.147865</v>
       </c>
-      <c r="O41" s="7">
+      <c r="O41" s="6">
         <v>43.549667</v>
       </c>
-      <c r="P41" s="7">
+      <c r="P41" s="6">
         <v>43.312492</v>
       </c>
     </row>
@@ -3439,46 +3435,46 @@
       <c r="A42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>71.5172</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="6">
         <v>104.773</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>90.148361</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="6">
         <v>90.178848</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="6">
         <v>99.265945</v>
       </c>
       <c r="G42" s="6">
         <v>70.800751</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="6">
         <v>79.711472</v>
       </c>
       <c r="I42" s="4">
         <v>64</v>
       </c>
-      <c r="J42" s="7">
+      <c r="J42" s="6">
         <v>35.094</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="6">
         <v>32.4122</v>
       </c>
-      <c r="L42" s="7">
+      <c r="L42" s="6">
         <v>51.621063</v>
       </c>
-      <c r="M42" s="7">
+      <c r="M42" s="6">
         <v>46.972603</v>
       </c>
-      <c r="N42" s="7">
+      <c r="N42" s="6">
         <v>51.086483</v>
       </c>
-      <c r="O42" s="7">
+      <c r="O42" s="6">
         <v>57.686352</v>
       </c>
       <c r="P42" s="6">
@@ -3486,46 +3482,46 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="8"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="6">
         <v>0.395329</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>0.41613</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>0.42769</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="6">
         <v>0.412622</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="9">
         <v>0.396893</v>
       </c>
       <c r="G44" s="6">
         <v>0.374612</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="6">
         <v>0.402432</v>
       </c>
       <c r="I44" s="4">
@@ -3534,22 +3530,22 @@
       <c r="J44" s="6">
         <v>0.219035</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="6">
         <v>0.242831</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44" s="9">
         <v>0.251389</v>
       </c>
-      <c r="M44" s="10">
+      <c r="M44" s="9">
         <v>0.251384</v>
       </c>
-      <c r="N44" s="10">
+      <c r="N44" s="9">
         <v>0.248967</v>
       </c>
-      <c r="O44" s="10">
+      <c r="O44" s="9">
         <v>0.221035</v>
       </c>
-      <c r="P44" s="10">
+      <c r="P44" s="9">
         <v>0.22368</v>
       </c>
     </row>
@@ -3557,49 +3553,49 @@
       <c r="A45" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="6">
         <v>0.506921</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="6">
         <v>0.481659</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>0.530643</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="6">
         <v>0.555978</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="9">
         <v>0.518948</v>
       </c>
       <c r="G45" s="6">
         <v>0.450602</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="6">
         <v>0.485472</v>
       </c>
       <c r="I45" s="4">
         <v>8</v>
       </c>
-      <c r="J45" s="7">
+      <c r="J45" s="6">
         <v>0.302245</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45" s="6">
         <v>0.329022</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="9">
         <v>0.323874</v>
       </c>
-      <c r="M45" s="10">
+      <c r="M45" s="9">
         <v>0.32823</v>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="9">
         <v>0.332003</v>
       </c>
-      <c r="O45" s="11">
+      <c r="O45" s="9">
         <v>0.300186</v>
       </c>
-      <c r="P45" s="11">
+      <c r="P45" s="9">
         <v>0.301119</v>
       </c>
     </row>
@@ -3610,46 +3606,46 @@
       <c r="B46" s="6">
         <v>0.547092</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="6">
         <v>0.63339</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>0.637328</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="6">
         <v>0.583225</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="9">
         <v>0.570821</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="6">
         <v>0.560325</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="6">
         <v>0.562696</v>
       </c>
       <c r="I46" s="4">
         <v>8</v>
       </c>
-      <c r="J46" s="7">
+      <c r="J46" s="6">
         <v>0.458196</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K46" s="6">
         <v>0.467823</v>
       </c>
-      <c r="L46" s="10">
+      <c r="L46" s="9">
         <v>0.487053</v>
       </c>
-      <c r="M46" s="10">
+      <c r="M46" s="9">
         <v>0.482289</v>
       </c>
-      <c r="N46" s="11">
+      <c r="N46" s="9">
         <v>0.451525</v>
       </c>
-      <c r="O46" s="10">
+      <c r="O46" s="9">
         <v>0.47635</v>
       </c>
-      <c r="P46" s="10">
+      <c r="P46" s="9">
         <v>0.458797</v>
       </c>
     </row>
@@ -3657,22 +3653,22 @@
       <c r="A47" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="6">
         <v>0.469802</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="6">
         <v>0.479615</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="6">
         <v>0.526874</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="6">
         <v>0.487893</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="9">
         <v>0.493961</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="6">
         <v>0.47894</v>
       </c>
       <c r="H47" s="6">
@@ -3681,25 +3677,25 @@
       <c r="I47" s="4">
         <v>8</v>
       </c>
-      <c r="J47" s="7">
+      <c r="J47" s="6">
         <v>0.355885</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K47" s="6">
         <v>0.368308</v>
       </c>
-      <c r="L47" s="10">
+      <c r="L47" s="9">
         <v>0.370078</v>
       </c>
-      <c r="M47" s="10">
+      <c r="M47" s="9">
         <v>0.369359</v>
       </c>
-      <c r="N47" s="11">
+      <c r="N47" s="9">
         <v>0.344411</v>
       </c>
-      <c r="O47" s="11">
+      <c r="O47" s="9">
         <v>0.352766</v>
       </c>
-      <c r="P47" s="10">
+      <c r="P47" s="9">
         <v>0.358145</v>
       </c>
     </row>
@@ -3707,22 +3703,22 @@
       <c r="A48" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="6">
         <v>0.518058</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="6">
         <v>0.549513</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="6">
         <v>0.612942</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="6">
         <v>0.580038</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="9">
         <v>0.529119</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="6">
         <v>0.548156</v>
       </c>
       <c r="H48" s="6">
@@ -3734,22 +3730,22 @@
       <c r="J48" s="6">
         <v>0.325299</v>
       </c>
-      <c r="K48" s="7">
+      <c r="K48" s="6">
         <v>0.358995</v>
       </c>
-      <c r="L48" s="10">
+      <c r="L48" s="9">
         <v>0.363969</v>
       </c>
-      <c r="M48" s="10">
+      <c r="M48" s="9">
         <v>0.363337</v>
       </c>
-      <c r="N48" s="10">
+      <c r="N48" s="9">
         <v>0.371768</v>
       </c>
-      <c r="O48" s="10">
+      <c r="O48" s="9">
         <v>0.339519</v>
       </c>
-      <c r="P48" s="10">
+      <c r="P48" s="9">
         <v>0.383975</v>
       </c>
     </row>
@@ -3757,49 +3753,49 @@
       <c r="A49" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="6">
         <v>0.358436</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="6">
         <v>0.380903</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="6">
         <v>0.426964</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="6">
         <v>0.402788</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="9">
         <v>0.378948</v>
       </c>
       <c r="G49" s="6">
         <v>0.350185</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="6">
         <v>0.382408</v>
       </c>
       <c r="I49" s="4">
         <v>16</v>
       </c>
-      <c r="J49" s="7">
+      <c r="J49" s="6">
         <v>0.224893</v>
       </c>
-      <c r="K49" s="7">
+      <c r="K49" s="6">
         <v>0.231101</v>
       </c>
-      <c r="L49" s="10">
+      <c r="L49" s="9">
         <v>0.245108</v>
       </c>
-      <c r="M49" s="10">
+      <c r="M49" s="9">
         <v>0.244378</v>
       </c>
-      <c r="N49" s="11">
+      <c r="N49" s="9">
         <v>0.214618</v>
       </c>
-      <c r="O49" s="11">
+      <c r="O49" s="9">
         <v>0.204705</v>
       </c>
-      <c r="P49" s="11">
+      <c r="P49" s="9">
         <v>0.212545</v>
       </c>
     </row>
@@ -3807,49 +3803,49 @@
       <c r="A50" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="6">
         <v>0.482643</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="6">
         <v>0.494316</v>
       </c>
       <c r="D50" s="6">
         <v>0.475194</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="6">
         <v>0.487942</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="9">
         <v>0.478549</v>
       </c>
       <c r="G50" s="6">
         <v>0.476384</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="6">
         <v>0.530959</v>
       </c>
       <c r="I50" s="4">
         <v>16</v>
       </c>
-      <c r="J50" s="7">
+      <c r="J50" s="6">
         <v>0.312914</v>
       </c>
-      <c r="K50" s="7">
+      <c r="K50" s="6">
         <v>0.315899</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50" s="9">
         <v>0.330693</v>
       </c>
-      <c r="M50" s="10">
+      <c r="M50" s="9">
         <v>0.332884</v>
       </c>
-      <c r="N50" s="11">
+      <c r="N50" s="9">
         <v>0.30318</v>
       </c>
-      <c r="O50" s="11">
+      <c r="O50" s="9">
         <v>0.296502</v>
       </c>
-      <c r="P50" s="11">
+      <c r="P50" s="9">
         <v>0.288336</v>
       </c>
     </row>
@@ -3857,19 +3853,19 @@
       <c r="A51" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="6">
         <v>0.597893</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="6">
         <v>0.579314</v>
       </c>
       <c r="D51" s="6">
         <v>0.568279</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="6">
         <v>0.612606</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="9">
         <v>0.5687</v>
       </c>
       <c r="G51" s="6">
@@ -3884,22 +3880,22 @@
       <c r="J51" s="6">
         <v>0.442432</v>
       </c>
-      <c r="K51" s="7">
+      <c r="K51" s="6">
         <v>0.459693</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="9">
         <v>0.489386</v>
       </c>
-      <c r="M51" s="10">
+      <c r="M51" s="9">
         <v>0.478516</v>
       </c>
-      <c r="N51" s="10">
+      <c r="N51" s="9">
         <v>0.453712</v>
       </c>
-      <c r="O51" s="10">
+      <c r="O51" s="9">
         <v>0.442676</v>
       </c>
-      <c r="P51" s="10">
+      <c r="P51" s="9">
         <v>0.443146</v>
       </c>
     </row>
@@ -3907,49 +3903,49 @@
       <c r="A52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="6">
         <v>0.453421</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="6">
         <v>0.521655</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="6">
         <v>0.512713</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="6">
         <v>0.474233</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="9">
         <v>0.479624</v>
       </c>
       <c r="G52" s="6">
         <v>0.427361</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="6">
         <v>0.482289</v>
       </c>
       <c r="I52" s="4">
         <v>16</v>
       </c>
-      <c r="J52" s="7">
+      <c r="J52" s="6">
         <v>0.342578</v>
       </c>
-      <c r="K52" s="7">
+      <c r="K52" s="6">
         <v>0.346486</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52" s="9">
         <v>0.353282</v>
       </c>
-      <c r="M52" s="10">
+      <c r="M52" s="9">
         <v>0.35346</v>
       </c>
-      <c r="N52" s="11">
+      <c r="N52" s="9">
         <v>0.338712</v>
       </c>
-      <c r="O52" s="11">
+      <c r="O52" s="9">
         <v>0.341556</v>
       </c>
-      <c r="P52" s="10">
+      <c r="P52" s="9">
         <v>0.349303</v>
       </c>
     </row>
@@ -3957,19 +3953,19 @@
       <c r="A53" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="6">
         <v>0.542482</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="6">
         <v>0.52175</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="6">
         <v>0.541503</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>0.533458</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="9">
         <v>0.577981</v>
       </c>
       <c r="G53" s="6">
@@ -3981,25 +3977,25 @@
       <c r="I53" s="4">
         <v>16</v>
       </c>
-      <c r="J53" s="7">
+      <c r="J53" s="6">
         <v>0.366711</v>
       </c>
-      <c r="K53" s="7">
+      <c r="K53" s="6">
         <v>0.356044</v>
       </c>
-      <c r="L53" s="11">
+      <c r="L53" s="9">
         <v>0.35323</v>
       </c>
-      <c r="M53" s="11">
+      <c r="M53" s="9">
         <v>0.354524</v>
       </c>
-      <c r="N53" s="10">
+      <c r="N53" s="9">
         <v>0.365759</v>
       </c>
-      <c r="O53" s="11">
+      <c r="O53" s="9">
         <v>0.330362</v>
       </c>
-      <c r="P53" s="11">
+      <c r="P53" s="9">
         <v>0.331466</v>
       </c>
     </row>
@@ -4007,10 +4003,10 @@
       <c r="A54" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="6">
         <v>0.376429</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="6">
         <v>0.389039</v>
       </c>
       <c r="D54" s="6">
@@ -4019,7 +4015,7 @@
       <c r="E54" s="6">
         <v>0.367606</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="9">
         <v>0.370823</v>
       </c>
       <c r="G54" s="6">
@@ -4034,22 +4030,22 @@
       <c r="J54" s="6">
         <v>0.207265</v>
       </c>
-      <c r="K54" s="7">
+      <c r="K54" s="6">
         <v>0.22899</v>
       </c>
-      <c r="L54" s="10">
+      <c r="L54" s="9">
         <v>0.23316</v>
       </c>
-      <c r="M54" s="10">
+      <c r="M54" s="9">
         <v>0.239269</v>
       </c>
-      <c r="N54" s="10">
+      <c r="N54" s="9">
         <v>0.230312</v>
       </c>
-      <c r="O54" s="10">
+      <c r="O54" s="9">
         <v>0.218418</v>
       </c>
-      <c r="P54" s="10">
+      <c r="P54" s="9">
         <v>0.219033</v>
       </c>
     </row>
@@ -4057,19 +4053,19 @@
       <c r="A55" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>0.448894</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="6">
         <v>0.50227</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>0.470322</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="6">
         <v>0.502254</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="9">
         <v>0.433948</v>
       </c>
       <c r="G55" s="6">
@@ -4081,25 +4077,25 @@
       <c r="I55" s="4">
         <v>32</v>
       </c>
-      <c r="J55" s="7">
+      <c r="J55" s="6">
         <v>0.307575</v>
       </c>
-      <c r="K55" s="7">
+      <c r="K55" s="6">
         <v>0.331968</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="9">
         <v>0.329158</v>
       </c>
-      <c r="M55" s="10">
+      <c r="M55" s="9">
         <v>0.321393</v>
       </c>
-      <c r="N55" s="10">
+      <c r="N55" s="9">
         <v>0.30938</v>
       </c>
-      <c r="O55" s="11">
+      <c r="O55" s="9">
         <v>0.295791</v>
       </c>
-      <c r="P55" s="11">
+      <c r="P55" s="9">
         <v>0.301354</v>
       </c>
     </row>
@@ -4107,19 +4103,19 @@
       <c r="A56" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="6">
         <v>0.564379</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="6">
         <v>0.562327</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>0.603746</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="6">
         <v>0.59088</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="9">
         <v>0.56588</v>
       </c>
       <c r="G56" s="6">
@@ -4131,25 +4127,25 @@
       <c r="I56" s="4">
         <v>32</v>
       </c>
-      <c r="J56" s="7">
+      <c r="J56" s="6">
         <v>0.434837</v>
       </c>
-      <c r="K56" s="7">
+      <c r="K56" s="6">
         <v>0.460331</v>
       </c>
-      <c r="L56" s="10">
+      <c r="L56" s="9">
         <v>0.461039</v>
       </c>
-      <c r="M56" s="10">
+      <c r="M56" s="9">
         <v>0.465491</v>
       </c>
-      <c r="N56" s="10">
+      <c r="N56" s="9">
         <v>0.464851</v>
       </c>
-      <c r="O56" s="10">
+      <c r="O56" s="9">
         <v>0.445543</v>
       </c>
-      <c r="P56" s="11">
+      <c r="P56" s="9">
         <v>0.434002</v>
       </c>
     </row>
@@ -4157,22 +4153,22 @@
       <c r="A57" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="6">
         <v>0.455148</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="6">
         <v>0.509024</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="6">
         <v>0.494772</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="6">
         <v>0.475748</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="9">
         <v>0.46694</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="6">
         <v>0.482703</v>
       </c>
       <c r="H57" s="6">
@@ -4181,25 +4177,25 @@
       <c r="I57" s="4">
         <v>32</v>
       </c>
-      <c r="J57" s="7">
+      <c r="J57" s="6">
         <v>0.343416</v>
       </c>
-      <c r="K57" s="7">
+      <c r="K57" s="6">
         <v>0.345455</v>
       </c>
-      <c r="L57" s="10">
+      <c r="L57" s="9">
         <v>0.362259</v>
       </c>
-      <c r="M57" s="10">
+      <c r="M57" s="9">
         <v>0.365292</v>
       </c>
-      <c r="N57" s="10">
+      <c r="N57" s="9">
         <v>0.370821</v>
       </c>
-      <c r="O57" s="10">
+      <c r="O57" s="9">
         <v>0.344146</v>
       </c>
-      <c r="P57" s="11">
+      <c r="P57" s="9">
         <v>0.320221</v>
       </c>
     </row>
@@ -4210,22 +4206,22 @@
       <c r="B58" s="6">
         <v>0.446245</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="6">
         <v>0.573886</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="9">
         <v>0.499958</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="9">
         <v>0.522259</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58" s="9">
         <v>0.508471</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="9">
         <v>0.465147</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="6">
         <v>0.521128</v>
       </c>
       <c r="I58" s="4">
@@ -4234,22 +4230,22 @@
       <c r="J58" s="6">
         <v>0.326931</v>
       </c>
-      <c r="K58" s="7">
+      <c r="K58" s="6">
         <v>0.348563</v>
       </c>
-      <c r="L58" s="10">
+      <c r="L58" s="9">
         <v>0.34662</v>
       </c>
-      <c r="M58" s="10">
+      <c r="M58" s="9">
         <v>0.342645</v>
       </c>
-      <c r="N58" s="10">
+      <c r="N58" s="9">
         <v>0.336251</v>
       </c>
-      <c r="O58" s="10">
+      <c r="O58" s="9">
         <v>0.377175</v>
       </c>
-      <c r="P58" s="10">
+      <c r="P58" s="9">
         <v>0.369383</v>
       </c>
     </row>
@@ -4257,22 +4253,22 @@
       <c r="A59" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="6">
         <v>0.349116</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="6">
         <v>0.325471</v>
       </c>
       <c r="D59" s="6">
         <v>0.312085</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="6">
         <v>0.386189</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59" s="9">
         <v>0.378238</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="6">
         <v>0.352447</v>
       </c>
       <c r="H59" s="6">
@@ -4281,25 +4277,25 @@
       <c r="I59" s="4">
         <v>64</v>
       </c>
-      <c r="J59" s="7">
+      <c r="J59" s="6">
         <v>0.21302</v>
       </c>
-      <c r="K59" s="7">
+      <c r="K59" s="6">
         <v>0.227093</v>
       </c>
-      <c r="L59" s="10">
+      <c r="L59" s="9">
         <v>0.230821</v>
       </c>
-      <c r="M59" s="10">
+      <c r="M59" s="9">
         <v>0.233263</v>
       </c>
-      <c r="N59" s="10">
+      <c r="N59" s="9">
         <v>0.214873</v>
       </c>
-      <c r="O59" s="11">
+      <c r="O59" s="9">
         <v>0.209941</v>
       </c>
-      <c r="P59" s="10">
+      <c r="P59" s="9">
         <v>0.232613</v>
       </c>
     </row>
@@ -4307,25 +4303,25 @@
       <c r="A60" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="6">
         <v>0.509603</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="6">
         <v>0.448351</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="6">
         <v>0.467041</v>
       </c>
       <c r="E60" s="6">
         <v>0.425036</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="9">
         <v>0.417391</v>
       </c>
       <c r="G60" s="6">
         <v>0.432181</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="6">
         <v>0.470415</v>
       </c>
       <c r="I60" s="4">
@@ -4334,22 +4330,22 @@
       <c r="J60" s="6">
         <v>0.302262</v>
       </c>
-      <c r="K60" s="7">
+      <c r="K60" s="6">
         <v>0.317197</v>
       </c>
-      <c r="L60" s="10">
+      <c r="L60" s="9">
         <v>0.320467</v>
       </c>
-      <c r="M60" s="10">
+      <c r="M60" s="9">
         <v>0.312985</v>
       </c>
-      <c r="N60" s="10">
+      <c r="N60" s="9">
         <v>0.310579</v>
       </c>
-      <c r="O60" s="10">
+      <c r="O60" s="9">
         <v>0.322213</v>
       </c>
-      <c r="P60" s="10">
+      <c r="P60" s="9">
         <v>0.305763</v>
       </c>
     </row>
@@ -4360,46 +4356,46 @@
       <c r="B61" s="6">
         <v>0.524409</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="6">
         <v>0.570377</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="6">
         <v>0.557012</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="6">
         <v>0.574679</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F61" s="9">
         <v>0.527036</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="6">
         <v>0.546377</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="6">
         <v>0.526461</v>
       </c>
       <c r="I61" s="4">
         <v>64</v>
       </c>
-      <c r="J61" s="7">
+      <c r="J61" s="6">
         <v>0.450167</v>
       </c>
       <c r="K61" s="6">
         <v>0.448644</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61" s="9">
         <v>0.47735</v>
       </c>
-      <c r="M61" s="10">
+      <c r="M61" s="9">
         <v>0.466392</v>
       </c>
-      <c r="N61" s="10">
+      <c r="N61" s="9">
         <v>0.450545</v>
       </c>
-      <c r="O61" s="10">
+      <c r="O61" s="9">
         <v>0.451046</v>
       </c>
-      <c r="P61" s="10">
+      <c r="P61" s="9">
         <v>0.454488</v>
       </c>
     </row>
@@ -4407,25 +4403,25 @@
       <c r="A62" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="6">
         <v>0.4297</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="6">
         <v>0.465089</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="6">
         <v>0.464257</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="6">
         <v>0.480182</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62" s="9">
         <v>0.44549</v>
       </c>
       <c r="G62" s="6">
         <v>0.415216</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="6">
         <v>0.464826</v>
       </c>
       <c r="I62" s="4">
@@ -4434,22 +4430,22 @@
       <c r="J62" s="6">
         <v>0.333444</v>
       </c>
-      <c r="K62" s="7">
+      <c r="K62" s="6">
         <v>0.351657</v>
       </c>
-      <c r="L62" s="10">
+      <c r="L62" s="9">
         <v>0.350538</v>
       </c>
-      <c r="M62" s="10">
+      <c r="M62" s="9">
         <v>0.348241</v>
       </c>
-      <c r="N62" s="10">
+      <c r="N62" s="9">
         <v>0.366594</v>
       </c>
-      <c r="O62" s="10">
+      <c r="O62" s="9">
         <v>0.345765</v>
       </c>
-      <c r="P62" s="10">
+      <c r="P62" s="9">
         <v>0.336885</v>
       </c>
     </row>
@@ -4457,84 +4453,84 @@
       <c r="A63" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="6">
         <v>0.492298</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="6">
         <v>0.512086</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="6">
         <v>0.513181</v>
       </c>
       <c r="E63" s="6">
         <v>0.484546</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63" s="9">
         <v>0.49852</v>
       </c>
       <c r="G63" s="6">
         <v>0.479691</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="9">
         <v>0.470381</v>
       </c>
       <c r="I63" s="4">
         <v>64</v>
       </c>
-      <c r="J63" s="7">
+      <c r="J63" s="6">
         <v>0.365454</v>
       </c>
-      <c r="K63" s="7">
+      <c r="K63" s="6">
         <v>0.354911</v>
       </c>
-      <c r="L63" s="10">
+      <c r="L63" s="9">
         <v>0.38697</v>
       </c>
-      <c r="M63" s="10">
+      <c r="M63" s="9">
         <v>0.365737</v>
       </c>
-      <c r="N63" s="11">
+      <c r="N63" s="9">
         <v>0.349503</v>
       </c>
-      <c r="O63" s="11">
+      <c r="O63" s="9">
         <v>0.342198</v>
       </c>
-      <c r="P63" s="11">
+      <c r="P63" s="9">
         <v>0.329494</v>
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="8"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="9"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="9"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="8"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="6">
         <v>0.107062</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="6">
         <v>0.107295</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="6">
         <v>0.112275</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="6">
         <v>0.109629</v>
       </c>
       <c r="F65" s="6">
@@ -4549,19 +4545,19 @@
       <c r="I65" s="4">
         <v>8</v>
       </c>
-      <c r="J65" s="7">
+      <c r="J65" s="6">
         <v>0.0956973</v>
       </c>
-      <c r="K65" s="7">
+      <c r="K65" s="6">
         <v>0.112076</v>
       </c>
-      <c r="L65" s="7">
+      <c r="L65" s="6">
         <v>0.110787</v>
       </c>
-      <c r="M65" s="7">
+      <c r="M65" s="6">
         <v>0.109784</v>
       </c>
-      <c r="N65" s="7">
+      <c r="N65" s="6">
         <v>0.107476</v>
       </c>
       <c r="O65" s="6">
@@ -4578,46 +4574,46 @@
       <c r="B66" s="6">
         <v>0.100639</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="6">
         <v>0.130126</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="6">
         <v>0.118322</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="6">
         <v>0.116254</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="6">
         <v>0.110254</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G66" s="6">
         <v>0.101335</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H66" s="6">
         <v>0.106804</v>
       </c>
       <c r="I66" s="4">
         <v>8</v>
       </c>
-      <c r="J66" s="7">
+      <c r="J66" s="6">
         <v>0.0980542</v>
       </c>
-      <c r="K66" s="7">
+      <c r="K66" s="6">
         <v>0.108958</v>
       </c>
-      <c r="L66" s="7">
+      <c r="L66" s="6">
         <v>0.112846</v>
       </c>
-      <c r="M66" s="7">
+      <c r="M66" s="6">
         <v>0.115152</v>
       </c>
-      <c r="N66" s="7">
+      <c r="N66" s="6">
         <v>0.105764</v>
       </c>
       <c r="O66" s="6">
         <v>0.096413</v>
       </c>
-      <c r="P66" s="7">
+      <c r="P66" s="6">
         <v>0.099686</v>
       </c>
     </row>
@@ -4628,22 +4624,22 @@
       <c r="B67" s="6">
         <v>0.0968898</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="6">
         <v>0.12161</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="6">
         <v>0.110691</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="6">
         <v>0.112955</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="6">
         <v>0.109587</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="6">
         <v>0.100492</v>
       </c>
-      <c r="H67" s="7">
+      <c r="H67" s="6">
         <v>0.098592</v>
       </c>
       <c r="I67" s="4">
@@ -4652,22 +4648,22 @@
       <c r="J67" s="6">
         <v>0.0946891</v>
       </c>
-      <c r="K67" s="7">
+      <c r="K67" s="6">
         <v>0.108117</v>
       </c>
-      <c r="L67" s="7">
+      <c r="L67" s="6">
         <v>0.107252</v>
       </c>
-      <c r="M67" s="7">
+      <c r="M67" s="6">
         <v>0.108014</v>
       </c>
-      <c r="N67" s="7">
+      <c r="N67" s="6">
         <v>0.101311</v>
       </c>
-      <c r="O67" s="7">
+      <c r="O67" s="6">
         <v>0.096143</v>
       </c>
-      <c r="P67" s="7">
+      <c r="P67" s="6">
         <v>0.096112</v>
       </c>
     </row>
@@ -4675,19 +4671,19 @@
       <c r="A68" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="6">
         <v>0.105989</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="6">
         <v>0.113807</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="6">
         <v>0.116705</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="6">
         <v>0.115121</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="6">
         <v>0.106383</v>
       </c>
       <c r="G68" s="6">
@@ -4699,19 +4695,19 @@
       <c r="I68" s="4">
         <v>8</v>
       </c>
-      <c r="J68" s="7">
+      <c r="J68" s="6">
         <v>0.0992141</v>
       </c>
-      <c r="K68" s="7">
+      <c r="K68" s="6">
         <v>0.107973</v>
       </c>
-      <c r="L68" s="7">
+      <c r="L68" s="6">
         <v>0.113772</v>
       </c>
-      <c r="M68" s="7">
+      <c r="M68" s="6">
         <v>0.111831</v>
       </c>
-      <c r="N68" s="7">
+      <c r="N68" s="6">
         <v>0.106948</v>
       </c>
       <c r="O68" s="6">
@@ -4725,22 +4721,22 @@
       <c r="A69" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="6">
         <v>0.103745</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="6">
         <v>0.113184</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="6">
         <v>0.11782</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="6">
         <v>0.116884</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="6">
         <v>0.111045</v>
       </c>
-      <c r="G69" s="7">
+      <c r="G69" s="6">
         <v>0.10753</v>
       </c>
       <c r="H69" s="6">
@@ -4749,19 +4745,19 @@
       <c r="I69" s="4">
         <v>8</v>
       </c>
-      <c r="J69" s="7">
+      <c r="J69" s="6">
         <v>0.0992723</v>
       </c>
-      <c r="K69" s="7">
+      <c r="K69" s="6">
         <v>0.121515</v>
       </c>
-      <c r="L69" s="7">
+      <c r="L69" s="6">
         <v>0.109183</v>
       </c>
-      <c r="M69" s="7">
+      <c r="M69" s="6">
         <v>0.108107</v>
       </c>
-      <c r="N69" s="7">
+      <c r="N69" s="6">
         <v>0.110601</v>
       </c>
       <c r="O69" s="6">
@@ -4775,43 +4771,43 @@
       <c r="A70" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="6">
         <v>0.0921673</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="6">
         <v>0.111954</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="6">
         <v>0.111757</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="6">
         <v>0.111935</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="6">
         <v>0.102531</v>
       </c>
       <c r="G70" s="6">
         <v>0.090881</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="6">
         <v>0.093097</v>
       </c>
       <c r="I70" s="4">
         <v>16</v>
       </c>
-      <c r="J70" s="7">
+      <c r="J70" s="6">
         <v>0.0990026</v>
       </c>
-      <c r="K70" s="7">
+      <c r="K70" s="6">
         <v>0.108744</v>
       </c>
-      <c r="L70" s="7">
+      <c r="L70" s="6">
         <v>0.107179</v>
       </c>
-      <c r="M70" s="7">
+      <c r="M70" s="6">
         <v>0.104523</v>
       </c>
-      <c r="N70" s="7">
+      <c r="N70" s="6">
         <v>0.099636</v>
       </c>
       <c r="O70" s="6">
@@ -4828,19 +4824,19 @@
       <c r="B71" s="6">
         <v>0.100524</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="6">
         <v>0.111732</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="6">
         <v>0.121122</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="6">
         <v>0.121109</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="6">
         <v>0.111959</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="6">
         <v>0.102785</v>
       </c>
       <c r="H71" s="6">
@@ -4849,25 +4845,25 @@
       <c r="I71" s="4">
         <v>16</v>
       </c>
-      <c r="J71" s="7">
+      <c r="J71" s="6">
         <v>0.0987882</v>
       </c>
-      <c r="K71" s="7">
+      <c r="K71" s="6">
         <v>0.106184</v>
       </c>
-      <c r="L71" s="7">
+      <c r="L71" s="6">
         <v>0.109442</v>
       </c>
-      <c r="M71" s="7">
+      <c r="M71" s="6">
         <v>0.108129</v>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="6">
         <v>0.103435</v>
       </c>
       <c r="O71" s="6">
         <v>0.097371</v>
       </c>
-      <c r="P71" s="7">
+      <c r="P71" s="6">
         <v>0.100348</v>
       </c>
     </row>
@@ -4875,49 +4871,49 @@
       <c r="A72" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="6">
         <v>0.0958475</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="6">
         <v>0.113758</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="6">
         <v>0.110448</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="6">
         <v>0.110838</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="6">
         <v>0.108175</v>
       </c>
       <c r="G72" s="6">
         <v>0.09569</v>
       </c>
-      <c r="H72" s="7">
+      <c r="H72" s="6">
         <v>0.10371</v>
       </c>
       <c r="I72" s="4">
         <v>16</v>
       </c>
-      <c r="J72" s="7">
+      <c r="J72" s="6">
         <v>0.0917235</v>
       </c>
-      <c r="K72" s="7">
+      <c r="K72" s="6">
         <v>0.106202</v>
       </c>
-      <c r="L72" s="7">
+      <c r="L72" s="6">
         <v>0.10847</v>
       </c>
-      <c r="M72" s="7">
+      <c r="M72" s="6">
         <v>0.107868</v>
       </c>
-      <c r="N72" s="7">
+      <c r="N72" s="6">
         <v>0.103217</v>
       </c>
       <c r="O72" s="6">
         <v>0.090251</v>
       </c>
-      <c r="P72" s="7">
+      <c r="P72" s="6">
         <v>0.092745</v>
       </c>
     </row>
@@ -4928,46 +4924,46 @@
       <c r="B73" s="6">
         <v>0.094055</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="6">
         <v>0.126262</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="6">
         <v>0.120301</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E73" s="6">
         <v>0.120404</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73" s="6">
         <v>0.107932</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G73" s="6">
         <v>0.094146</v>
       </c>
-      <c r="H73" s="7">
+      <c r="H73" s="6">
         <v>0.094506</v>
       </c>
       <c r="I73" s="4">
         <v>16</v>
       </c>
-      <c r="J73" s="7">
+      <c r="J73" s="6">
         <v>0.0974393</v>
       </c>
-      <c r="K73" s="7">
+      <c r="K73" s="6">
         <v>0.112597</v>
       </c>
-      <c r="L73" s="7">
+      <c r="L73" s="6">
         <v>0.115772</v>
       </c>
-      <c r="M73" s="7">
+      <c r="M73" s="6">
         <v>0.115937</v>
       </c>
-      <c r="N73" s="7">
+      <c r="N73" s="6">
         <v>0.103376</v>
       </c>
       <c r="O73" s="6">
         <v>0.095704</v>
       </c>
-      <c r="P73" s="7">
+      <c r="P73" s="6">
         <v>0.099697</v>
       </c>
     </row>
@@ -4975,19 +4971,19 @@
       <c r="A74" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="6">
         <v>0.107528</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="6">
         <v>0.1158</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="6">
         <v>0.116467</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="6">
         <v>0.116686</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="6">
         <v>0.118816</v>
       </c>
       <c r="G74" s="6">
@@ -5002,22 +4998,22 @@
       <c r="J74" s="6">
         <v>0.0945558</v>
       </c>
-      <c r="K74" s="7">
+      <c r="K74" s="6">
         <v>0.106906</v>
       </c>
-      <c r="L74" s="7">
+      <c r="L74" s="6">
         <v>0.111553</v>
       </c>
-      <c r="M74" s="7">
+      <c r="M74" s="6">
         <v>0.109653</v>
       </c>
-      <c r="N74" s="7">
+      <c r="N74" s="6">
         <v>0.10521</v>
       </c>
-      <c r="O74" s="7">
+      <c r="O74" s="6">
         <v>0.094938</v>
       </c>
-      <c r="P74" s="7">
+      <c r="P74" s="6">
         <v>0.097694</v>
       </c>
     </row>
@@ -5028,22 +5024,22 @@
       <c r="B75" s="6">
         <v>0.0901184</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="6">
         <v>0.112141</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="6">
         <v>0.10989</v>
       </c>
-      <c r="E75" s="7">
+      <c r="E75" s="6">
         <v>0.109871</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75" s="6">
         <v>0.107759</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="6">
         <v>0.103928</v>
       </c>
-      <c r="H75" s="7">
+      <c r="H75" s="6">
         <v>0.098455</v>
       </c>
       <c r="I75" s="4">
@@ -5052,22 +5048,22 @@
       <c r="J75" s="6">
         <v>0.0943139</v>
       </c>
-      <c r="K75" s="7">
+      <c r="K75" s="6">
         <v>0.107687</v>
       </c>
-      <c r="L75" s="7">
+      <c r="L75" s="6">
         <v>0.107675</v>
       </c>
-      <c r="M75" s="7">
+      <c r="M75" s="6">
         <v>0.106718</v>
       </c>
-      <c r="N75" s="7">
+      <c r="N75" s="6">
         <v>0.105622</v>
       </c>
-      <c r="O75" s="7">
+      <c r="O75" s="6">
         <v>0.094393</v>
       </c>
-      <c r="P75" s="7">
+      <c r="P75" s="6">
         <v>0.096067</v>
       </c>
     </row>
@@ -5075,25 +5071,25 @@
       <c r="A76" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="6">
         <v>0.100188</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="6">
         <v>0.113419</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="6">
         <v>0.125977</v>
       </c>
-      <c r="E76" s="7">
+      <c r="E76" s="6">
         <v>0.126276</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="6">
         <v>0.115382</v>
       </c>
       <c r="G76" s="6">
         <v>0.099977</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="6">
         <v>0.101982</v>
       </c>
       <c r="I76" s="4">
@@ -5102,22 +5098,22 @@
       <c r="J76" s="6">
         <v>0.0959092</v>
       </c>
-      <c r="K76" s="7">
+      <c r="K76" s="6">
         <v>0.109527</v>
       </c>
-      <c r="L76" s="7">
+      <c r="L76" s="6">
         <v>0.108156</v>
       </c>
-      <c r="M76" s="7">
+      <c r="M76" s="6">
         <v>0.106453</v>
       </c>
-      <c r="N76" s="7">
+      <c r="N76" s="6">
         <v>0.100886</v>
       </c>
-      <c r="O76" s="7">
+      <c r="O76" s="6">
         <v>0.098281</v>
       </c>
-      <c r="P76" s="7">
+      <c r="P76" s="6">
         <v>0.096954</v>
       </c>
     </row>
@@ -5125,22 +5121,22 @@
       <c r="A77" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="6">
         <v>0.0954529</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="6">
         <v>0.118074</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="6">
         <v>0.106928</v>
       </c>
-      <c r="E77" s="7">
+      <c r="E77" s="6">
         <v>0.106985</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="6">
         <v>0.115639</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="6">
         <v>0.096888</v>
       </c>
       <c r="H77" s="6">
@@ -5149,19 +5145,19 @@
       <c r="I77" s="4">
         <v>32</v>
       </c>
-      <c r="J77" s="7">
+      <c r="J77" s="6">
         <v>0.0916943</v>
       </c>
-      <c r="K77" s="7">
+      <c r="K77" s="6">
         <v>0.099657</v>
       </c>
-      <c r="L77" s="7">
+      <c r="L77" s="6">
         <v>0.102066</v>
       </c>
-      <c r="M77" s="7">
+      <c r="M77" s="6">
         <v>0.106138</v>
       </c>
-      <c r="N77" s="7">
+      <c r="N77" s="6">
         <v>0.105403</v>
       </c>
       <c r="O77" s="6">
@@ -5178,22 +5174,22 @@
       <c r="B78" s="6">
         <v>0.0897157</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="6">
         <v>0.109722</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="6">
         <v>0.109564</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E78" s="6">
         <v>0.109544</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="6">
         <v>0.112276</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G78" s="6">
         <v>0.093705</v>
       </c>
-      <c r="H78" s="7">
+      <c r="H78" s="6">
         <v>0.091969</v>
       </c>
       <c r="I78" s="4">
@@ -5202,22 +5198,22 @@
       <c r="J78" s="6">
         <v>0.0932576</v>
       </c>
-      <c r="K78" s="7">
+      <c r="K78" s="6">
         <v>0.105964</v>
       </c>
-      <c r="L78" s="7">
+      <c r="L78" s="6">
         <v>0.110416</v>
       </c>
-      <c r="M78" s="7">
+      <c r="M78" s="6">
         <v>0.111017</v>
       </c>
-      <c r="N78" s="7">
+      <c r="N78" s="6">
         <v>0.106785</v>
       </c>
-      <c r="O78" s="7">
+      <c r="O78" s="6">
         <v>0.09702</v>
       </c>
-      <c r="P78" s="7">
+      <c r="P78" s="6">
         <v>0.097149</v>
       </c>
     </row>
@@ -5225,19 +5221,19 @@
       <c r="A79" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="6">
         <v>0.101574</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="6">
         <v>0.115499</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="6">
         <v>0.11993</v>
       </c>
-      <c r="E79" s="7">
+      <c r="E79" s="6">
         <v>0.119956</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="6">
         <v>0.113233</v>
       </c>
       <c r="G79" s="6">
@@ -5249,25 +5245,25 @@
       <c r="I79" s="4">
         <v>32</v>
       </c>
-      <c r="J79" s="7">
+      <c r="J79" s="6">
         <v>0.0924016</v>
       </c>
-      <c r="K79" s="7">
+      <c r="K79" s="6">
         <v>0.109792</v>
       </c>
-      <c r="L79" s="7">
+      <c r="L79" s="6">
         <v>0.110215</v>
       </c>
-      <c r="M79" s="7">
+      <c r="M79" s="6">
         <v>0.108999</v>
       </c>
-      <c r="N79" s="7">
+      <c r="N79" s="6">
         <v>0.106559</v>
       </c>
       <c r="O79" s="6">
         <v>0.091913</v>
       </c>
-      <c r="P79" s="7">
+      <c r="P79" s="6">
         <v>0.095427</v>
       </c>
     </row>
@@ -5275,19 +5271,19 @@
       <c r="A80" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="6">
         <v>0.100896</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="6">
         <v>0.109719</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="6">
         <v>0.111665</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E80" s="6">
         <v>0.111776</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="6">
         <v>0.112559</v>
       </c>
       <c r="G80" s="6">
@@ -5302,22 +5298,22 @@
       <c r="J80" s="6">
         <v>0.0911824</v>
       </c>
-      <c r="K80" s="7">
+      <c r="K80" s="6">
         <v>0.107125</v>
       </c>
-      <c r="L80" s="7">
+      <c r="L80" s="6">
         <v>0.10667</v>
       </c>
-      <c r="M80" s="7">
+      <c r="M80" s="6">
         <v>0.10533</v>
       </c>
-      <c r="N80" s="7">
+      <c r="N80" s="6">
         <v>0.104074</v>
       </c>
-      <c r="O80" s="7">
+      <c r="O80" s="6">
         <v>0.09656</v>
       </c>
-      <c r="P80" s="7">
+      <c r="P80" s="6">
         <v>0.096473</v>
       </c>
     </row>
@@ -5325,19 +5321,19 @@
       <c r="A81" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="6">
         <v>0.10547</v>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="6">
         <v>0.114586</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="6">
         <v>0.119549</v>
       </c>
-      <c r="E81" s="7">
+      <c r="E81" s="6">
         <v>0.119589</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="6">
         <v>0.115538</v>
       </c>
       <c r="G81" s="6">
@@ -5349,25 +5345,25 @@
       <c r="I81" s="4">
         <v>64</v>
       </c>
-      <c r="J81" s="7">
+      <c r="J81" s="6">
         <v>0.0962845</v>
       </c>
-      <c r="K81" s="7">
+      <c r="K81" s="6">
         <v>0.108977</v>
       </c>
-      <c r="L81" s="7">
+      <c r="L81" s="6">
         <v>0.107265</v>
       </c>
-      <c r="M81" s="7">
+      <c r="M81" s="6">
         <v>0.108449</v>
       </c>
-      <c r="N81" s="7">
+      <c r="N81" s="6">
         <v>0.104427</v>
       </c>
       <c r="O81" s="6">
         <v>0.095632</v>
       </c>
-      <c r="P81" s="7">
+      <c r="P81" s="6">
         <v>0.09874</v>
       </c>
     </row>
@@ -5378,22 +5374,22 @@
       <c r="B82" s="6">
         <v>0.0936792</v>
       </c>
-      <c r="C82" s="7">
+      <c r="C82" s="6">
         <v>0.109511</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="6">
         <v>0.110822</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E82" s="6">
         <v>0.110878</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="6">
         <v>0.110867</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G82" s="6">
         <v>0.095028</v>
       </c>
-      <c r="H82" s="7">
+      <c r="H82" s="6">
         <v>0.093947</v>
       </c>
       <c r="I82" s="4">
@@ -5402,22 +5398,22 @@
       <c r="J82" s="6">
         <v>0.0913756</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K82" s="6">
         <v>0.104472</v>
       </c>
-      <c r="L82" s="7">
+      <c r="L82" s="6">
         <v>0.104541</v>
       </c>
-      <c r="M82" s="7">
+      <c r="M82" s="6">
         <v>0.103858</v>
       </c>
-      <c r="N82" s="7">
+      <c r="N82" s="6">
         <v>0.106179</v>
       </c>
-      <c r="O82" s="7">
+      <c r="O82" s="6">
         <v>0.09452</v>
       </c>
-      <c r="P82" s="7">
+      <c r="P82" s="6">
         <v>0.09379</v>
       </c>
     </row>
@@ -5428,40 +5424,40 @@
       <c r="B83" s="6">
         <v>0.0934745</v>
       </c>
-      <c r="C83" s="7">
+      <c r="C83" s="6">
         <v>0.108998</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="6">
         <v>0.109956</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E83" s="6">
         <v>0.109945</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="6">
         <v>0.108697</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="6">
         <v>0.099028</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="6">
         <v>0.099089</v>
       </c>
       <c r="I83" s="4">
         <v>64</v>
       </c>
-      <c r="J83" s="7">
+      <c r="J83" s="6">
         <v>0.0986748</v>
       </c>
-      <c r="K83" s="7">
+      <c r="K83" s="6">
         <v>0.106726</v>
       </c>
-      <c r="L83" s="7">
+      <c r="L83" s="6">
         <v>0.111071</v>
       </c>
-      <c r="M83" s="7">
+      <c r="M83" s="6">
         <v>0.11374</v>
       </c>
-      <c r="N83" s="7">
+      <c r="N83" s="6">
         <v>0.105181</v>
       </c>
       <c r="O83" s="6">
@@ -5478,43 +5474,43 @@
       <c r="B84" s="6">
         <v>0.096221</v>
       </c>
-      <c r="C84" s="7">
+      <c r="C84" s="6">
         <v>0.115871</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="6">
         <v>0.117136</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E84" s="6">
         <v>0.117186</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="6">
         <v>0.122227</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="6">
         <v>0.098587</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H84" s="6">
         <v>0.098538</v>
       </c>
       <c r="I84" s="4">
         <v>64</v>
       </c>
-      <c r="J84" s="7">
+      <c r="J84" s="6">
         <v>0.0972475</v>
       </c>
-      <c r="K84" s="7">
+      <c r="K84" s="6">
         <v>0.111023</v>
       </c>
-      <c r="L84" s="7">
+      <c r="L84" s="6">
         <v>0.107966</v>
       </c>
-      <c r="M84" s="7">
+      <c r="M84" s="6">
         <v>0.109272</v>
       </c>
-      <c r="N84" s="7">
+      <c r="N84" s="6">
         <v>0.10588</v>
       </c>
-      <c r="O84" s="7">
+      <c r="O84" s="6">
         <v>0.100261</v>
       </c>
       <c r="P84" s="6">
@@ -5522,22 +5518,22 @@
       </c>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="8"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="9"/>
-      <c r="M85" s="9"/>
-      <c r="N85" s="9"/>
-      <c r="O85" s="9"/>
-      <c r="P85" s="9"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+      <c r="N85" s="8"/>
+      <c r="O85" s="8"/>
+      <c r="P85" s="8"/>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="4" t="s">
@@ -5546,22 +5542,22 @@
       <c r="B86" s="6">
         <v>0.0724391</v>
       </c>
-      <c r="C86" s="7">
+      <c r="C86" s="6">
         <v>0.0908768</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="6">
         <v>0.088112</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E86" s="6">
         <v>0.08811</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="6">
         <v>0.079723</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G86" s="6">
         <v>0.074617</v>
       </c>
-      <c r="H86" s="7">
+      <c r="H86" s="6">
         <v>0.074307</v>
       </c>
       <c r="I86" s="4">
@@ -5570,22 +5566,22 @@
       <c r="J86" s="6">
         <v>0.0662681</v>
       </c>
-      <c r="K86" s="7">
+      <c r="K86" s="6">
         <v>0.0731313</v>
       </c>
-      <c r="L86" s="7">
+      <c r="L86" s="6">
         <v>0.078358</v>
       </c>
-      <c r="M86" s="7">
+      <c r="M86" s="6">
         <v>0.081654</v>
       </c>
-      <c r="N86" s="7">
+      <c r="N86" s="6">
         <v>0.074283</v>
       </c>
-      <c r="O86" s="7">
+      <c r="O86" s="6">
         <v>0.067064</v>
       </c>
-      <c r="P86" s="7">
+      <c r="P86" s="6">
         <v>0.067122</v>
       </c>
     </row>
@@ -5596,46 +5592,46 @@
       <c r="B87" s="6">
         <v>0.0756642</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="6">
         <v>0.0929401</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="6">
         <v>0.093615</v>
       </c>
-      <c r="E87" s="7">
+      <c r="E87" s="6">
         <v>0.093844</v>
       </c>
-      <c r="F87" s="7">
+      <c r="F87" s="6">
         <v>0.08589</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="6">
         <v>0.075855</v>
       </c>
-      <c r="H87" s="7">
+      <c r="H87" s="6">
         <v>0.078311</v>
       </c>
       <c r="I87" s="4">
         <v>8</v>
       </c>
-      <c r="J87" s="7">
+      <c r="J87" s="6">
         <v>0.0686961</v>
       </c>
-      <c r="K87" s="7">
+      <c r="K87" s="6">
         <v>0.0775051</v>
       </c>
-      <c r="L87" s="7">
+      <c r="L87" s="6">
         <v>0.076242</v>
       </c>
-      <c r="M87" s="7">
+      <c r="M87" s="6">
         <v>0.077314</v>
       </c>
-      <c r="N87" s="7">
+      <c r="N87" s="6">
         <v>0.071129</v>
       </c>
       <c r="O87" s="6">
         <v>0.067591</v>
       </c>
-      <c r="P87" s="7">
+      <c r="P87" s="6">
         <v>0.069266</v>
       </c>
     </row>
@@ -5646,40 +5642,40 @@
       <c r="B88" s="6">
         <v>0.0690421</v>
       </c>
-      <c r="C88" s="7">
+      <c r="C88" s="6">
         <v>0.0866595</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="6">
         <v>0.08921</v>
       </c>
-      <c r="E88" s="7">
+      <c r="E88" s="6">
         <v>0.089591</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="6">
         <v>0.078249</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G88" s="6">
         <v>0.072534</v>
       </c>
-      <c r="H88" s="7">
+      <c r="H88" s="6">
         <v>0.06997</v>
       </c>
       <c r="I88" s="4">
         <v>8</v>
       </c>
-      <c r="J88" s="7">
+      <c r="J88" s="6">
         <v>0.0671213</v>
       </c>
-      <c r="K88" s="7">
+      <c r="K88" s="6">
         <v>0.0720732</v>
       </c>
-      <c r="L88" s="7">
+      <c r="L88" s="6">
         <v>0.073313</v>
       </c>
-      <c r="M88" s="7">
+      <c r="M88" s="6">
         <v>0.072671</v>
       </c>
-      <c r="N88" s="7">
+      <c r="N88" s="6">
         <v>0.068355</v>
       </c>
       <c r="O88" s="6">
@@ -5693,40 +5689,40 @@
       <c r="A89" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="6">
         <v>0.0740638</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="6">
         <v>0.0883557</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="6">
         <v>0.095514</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="6">
         <v>0.089703</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="6">
         <v>0.082952</v>
       </c>
       <c r="G89" s="6">
         <v>0.074006</v>
       </c>
-      <c r="H89" s="7">
+      <c r="H89" s="6">
         <v>0.078037</v>
       </c>
       <c r="I89" s="4">
         <v>8</v>
       </c>
-      <c r="J89" s="7">
+      <c r="J89" s="6">
         <v>0.0752314</v>
       </c>
-      <c r="K89" s="7">
+      <c r="K89" s="6">
         <v>0.0779216</v>
       </c>
-      <c r="L89" s="7">
+      <c r="L89" s="6">
         <v>0.085185</v>
       </c>
-      <c r="M89" s="7">
+      <c r="M89" s="6">
         <v>0.085574</v>
       </c>
       <c r="N89" s="6">
@@ -5743,22 +5739,22 @@
       <c r="A90" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="6">
         <v>0.0736715</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="6">
         <v>0.089593</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="6">
         <v>0.086936</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="6">
         <v>0.092062</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F90" s="6">
         <v>0.077547</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G90" s="6">
         <v>0.075013</v>
       </c>
       <c r="H90" s="6">
@@ -5767,19 +5763,19 @@
       <c r="I90" s="4">
         <v>8</v>
       </c>
-      <c r="J90" s="7">
+      <c r="J90" s="6">
         <v>0.0679202</v>
       </c>
-      <c r="K90" s="7">
+      <c r="K90" s="6">
         <v>0.0767993</v>
       </c>
-      <c r="L90" s="7">
+      <c r="L90" s="6">
         <v>0.074092</v>
       </c>
-      <c r="M90" s="7">
+      <c r="M90" s="6">
         <v>0.075563</v>
       </c>
-      <c r="N90" s="7">
+      <c r="N90" s="6">
         <v>0.074421</v>
       </c>
       <c r="O90" s="6">
@@ -5796,46 +5792,46 @@
       <c r="B91" s="6">
         <v>0.070492</v>
       </c>
-      <c r="C91" s="7">
+      <c r="C91" s="6">
         <v>0.0833101</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="6">
         <v>0.083317</v>
       </c>
-      <c r="E91" s="7">
+      <c r="E91" s="6">
         <v>0.084468</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F91" s="6">
         <v>0.076096</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G91" s="6">
         <v>0.07241</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H91" s="6">
         <v>0.070497</v>
       </c>
       <c r="I91" s="4">
         <v>16</v>
       </c>
-      <c r="J91" s="7">
+      <c r="J91" s="6">
         <v>0.0679345</v>
       </c>
-      <c r="K91" s="7">
+      <c r="K91" s="6">
         <v>0.0745854</v>
       </c>
-      <c r="L91" s="7">
+      <c r="L91" s="6">
         <v>0.076751</v>
       </c>
-      <c r="M91" s="7">
+      <c r="M91" s="6">
         <v>0.077596</v>
       </c>
-      <c r="N91" s="7">
+      <c r="N91" s="6">
         <v>0.074764</v>
       </c>
       <c r="O91" s="6">
         <v>0.065745</v>
       </c>
-      <c r="P91" s="7">
+      <c r="P91" s="6">
         <v>0.068236</v>
       </c>
     </row>
@@ -5843,49 +5839,49 @@
       <c r="A92" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="6">
         <v>0.0748661</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="6">
         <v>0.0862596</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="6">
         <v>0.09404</v>
       </c>
-      <c r="E92" s="7">
+      <c r="E92" s="6">
         <v>0.089013</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="6">
         <v>0.083731</v>
       </c>
       <c r="G92" s="6">
         <v>0.074756</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H92" s="6">
         <v>0.077321</v>
       </c>
       <c r="I92" s="4">
         <v>16</v>
       </c>
-      <c r="J92" s="7">
+      <c r="J92" s="6">
         <v>0.0682474</v>
       </c>
-      <c r="K92" s="7">
+      <c r="K92" s="6">
         <v>0.0723627</v>
       </c>
-      <c r="L92" s="7">
+      <c r="L92" s="6">
         <v>0.074695</v>
       </c>
-      <c r="M92" s="7">
+      <c r="M92" s="6">
         <v>0.073675</v>
       </c>
-      <c r="N92" s="7">
+      <c r="N92" s="6">
         <v>0.076074</v>
       </c>
       <c r="O92" s="6">
         <v>0.067779</v>
       </c>
-      <c r="P92" s="7">
+      <c r="P92" s="6">
         <v>0.070159</v>
       </c>
     </row>
@@ -5896,22 +5892,22 @@
       <c r="B93" s="6">
         <v>0.0701178</v>
       </c>
-      <c r="C93" s="7">
+      <c r="C93" s="6">
         <v>0.0844942</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="6">
         <v>0.083986</v>
       </c>
-      <c r="E93" s="7">
+      <c r="E93" s="6">
         <v>0.082317</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="6">
         <v>0.082181</v>
       </c>
-      <c r="G93" s="7">
+      <c r="G93" s="6">
         <v>0.0703</v>
       </c>
-      <c r="H93" s="7">
+      <c r="H93" s="6">
         <v>0.071663</v>
       </c>
       <c r="I93" s="4">
@@ -5920,22 +5916,22 @@
       <c r="J93" s="6">
         <v>0.0621615</v>
       </c>
-      <c r="K93" s="7">
+      <c r="K93" s="6">
         <v>0.0698293</v>
       </c>
-      <c r="L93" s="7">
+      <c r="L93" s="6">
         <v>0.073327</v>
       </c>
-      <c r="M93" s="7">
+      <c r="M93" s="6">
         <v>0.07368</v>
       </c>
-      <c r="N93" s="7">
+      <c r="N93" s="6">
         <v>0.071331</v>
       </c>
-      <c r="O93" s="7">
+      <c r="O93" s="6">
         <v>0.065864</v>
       </c>
-      <c r="P93" s="7">
+      <c r="P93" s="6">
         <v>0.066578</v>
       </c>
     </row>
@@ -5946,40 +5942,40 @@
       <c r="B94" s="6">
         <v>0.073624</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="6">
         <v>0.088333</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="6">
         <v>0.087478</v>
       </c>
-      <c r="E94" s="7">
+      <c r="E94" s="6">
         <v>0.085897</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F94" s="6">
         <v>0.084125</v>
       </c>
-      <c r="G94" s="7">
+      <c r="G94" s="6">
         <v>0.075263</v>
       </c>
-      <c r="H94" s="7">
+      <c r="H94" s="6">
         <v>0.076613</v>
       </c>
       <c r="I94" s="4">
         <v>16</v>
       </c>
-      <c r="J94" s="7">
+      <c r="J94" s="6">
         <v>0.0721549</v>
       </c>
-      <c r="K94" s="7">
+      <c r="K94" s="6">
         <v>0.0818147</v>
       </c>
-      <c r="L94" s="7">
+      <c r="L94" s="6">
         <v>0.081658</v>
       </c>
-      <c r="M94" s="7">
+      <c r="M94" s="6">
         <v>0.081232</v>
       </c>
-      <c r="N94" s="7">
+      <c r="N94" s="6">
         <v>0.07788</v>
       </c>
       <c r="O94" s="6">
@@ -5996,40 +5992,40 @@
       <c r="B95" s="6">
         <v>0.0706951</v>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="6">
         <v>0.0871691</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="6">
         <v>0.087266</v>
       </c>
-      <c r="E95" s="7">
+      <c r="E95" s="6">
         <v>0.088462</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F95" s="6">
         <v>0.081706</v>
       </c>
-      <c r="G95" s="7">
+      <c r="G95" s="6">
         <v>0.072981</v>
       </c>
-      <c r="H95" s="7">
+      <c r="H95" s="6">
         <v>0.075788</v>
       </c>
       <c r="I95" s="4">
         <v>16</v>
       </c>
-      <c r="J95" s="7">
+      <c r="J95" s="6">
         <v>0.0668516</v>
       </c>
-      <c r="K95" s="7">
+      <c r="K95" s="6">
         <v>0.0757822</v>
       </c>
-      <c r="L95" s="7">
+      <c r="L95" s="6">
         <v>0.075169</v>
       </c>
-      <c r="M95" s="7">
+      <c r="M95" s="6">
         <v>0.075241</v>
       </c>
-      <c r="N95" s="7">
+      <c r="N95" s="6">
         <v>0.073504</v>
       </c>
       <c r="O95" s="6">
@@ -6046,22 +6042,22 @@
       <c r="B96" s="6">
         <v>0.0680769</v>
       </c>
-      <c r="C96" s="7">
+      <c r="C96" s="6">
         <v>0.0815346</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="6">
         <v>0.083659</v>
       </c>
-      <c r="E96" s="7">
+      <c r="E96" s="6">
         <v>0.08365</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="6">
         <v>0.081017</v>
       </c>
-      <c r="G96" s="7">
+      <c r="G96" s="6">
         <v>0.068292</v>
       </c>
-      <c r="H96" s="7">
+      <c r="H96" s="6">
         <v>0.069793</v>
       </c>
       <c r="I96" s="4">
@@ -6070,22 +6066,22 @@
       <c r="J96" s="6">
         <v>0.0664299</v>
       </c>
-      <c r="K96" s="7">
+      <c r="K96" s="6">
         <v>0.0765122</v>
       </c>
-      <c r="L96" s="7">
+      <c r="L96" s="6">
         <v>0.072065</v>
       </c>
-      <c r="M96" s="7">
+      <c r="M96" s="6">
         <v>0.073887</v>
       </c>
-      <c r="N96" s="7">
+      <c r="N96" s="6">
         <v>0.071775</v>
       </c>
-      <c r="O96" s="7">
+      <c r="O96" s="6">
         <v>0.067541</v>
       </c>
-      <c r="P96" s="7">
+      <c r="P96" s="6">
         <v>0.06741</v>
       </c>
     </row>
@@ -6093,19 +6089,19 @@
       <c r="A97" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="6">
         <v>0.0768156</v>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="6">
         <v>0.0838583</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="6">
         <v>0.085168</v>
       </c>
-      <c r="E97" s="7">
+      <c r="E97" s="6">
         <v>0.085198</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F97" s="6">
         <v>0.086687</v>
       </c>
       <c r="G97" s="6">
@@ -6120,22 +6116,22 @@
       <c r="J97" s="6">
         <v>0.0652329</v>
       </c>
-      <c r="K97" s="7">
+      <c r="K97" s="6">
         <v>0.0719734</v>
       </c>
-      <c r="L97" s="7">
+      <c r="L97" s="6">
         <v>0.077158</v>
       </c>
-      <c r="M97" s="7">
+      <c r="M97" s="6">
         <v>0.075528</v>
       </c>
-      <c r="N97" s="7">
+      <c r="N97" s="6">
         <v>0.072518</v>
       </c>
-      <c r="O97" s="7">
+      <c r="O97" s="6">
         <v>0.06788</v>
       </c>
-      <c r="P97" s="7">
+      <c r="P97" s="6">
         <v>0.067083</v>
       </c>
     </row>
@@ -6143,19 +6139,19 @@
       <c r="A98" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="6">
         <v>0.0709826</v>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="6">
         <v>0.0820081</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="6">
         <v>0.081135</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E98" s="6">
         <v>0.081148</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F98" s="6">
         <v>0.079638</v>
       </c>
       <c r="G98" s="6">
@@ -6170,22 +6166,22 @@
       <c r="J98" s="6">
         <v>0.0624926</v>
       </c>
-      <c r="K98" s="7">
+      <c r="K98" s="6">
         <v>0.0671966</v>
       </c>
-      <c r="L98" s="7">
+      <c r="L98" s="6">
         <v>0.074251</v>
       </c>
-      <c r="M98" s="7">
+      <c r="M98" s="6">
         <v>0.074887</v>
       </c>
-      <c r="N98" s="7">
+      <c r="N98" s="6">
         <v>0.071252</v>
       </c>
-      <c r="O98" s="7">
+      <c r="O98" s="6">
         <v>0.063047</v>
       </c>
-      <c r="P98" s="7">
+      <c r="P98" s="6">
         <v>0.06476</v>
       </c>
     </row>
@@ -6196,22 +6192,22 @@
       <c r="B99" s="6">
         <v>0.0738107</v>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="6">
         <v>0.0887939</v>
       </c>
-      <c r="D99" s="7">
+      <c r="D99" s="6">
         <v>0.088631</v>
       </c>
-      <c r="E99" s="7">
+      <c r="E99" s="6">
         <v>0.08863</v>
       </c>
-      <c r="F99" s="7">
+      <c r="F99" s="6">
         <v>0.087272</v>
       </c>
-      <c r="G99" s="7">
+      <c r="G99" s="6">
         <v>0.074028</v>
       </c>
-      <c r="H99" s="7">
+      <c r="H99" s="6">
         <v>0.077062</v>
       </c>
       <c r="I99" s="4">
@@ -6220,22 +6216,22 @@
       <c r="J99" s="6">
         <v>0.0703713</v>
       </c>
-      <c r="K99" s="7">
+      <c r="K99" s="6">
         <v>0.0794725</v>
       </c>
-      <c r="L99" s="7">
+      <c r="L99" s="6">
         <v>0.081543</v>
       </c>
-      <c r="M99" s="7">
+      <c r="M99" s="6">
         <v>0.079333</v>
       </c>
-      <c r="N99" s="7">
+      <c r="N99" s="6">
         <v>0.081822</v>
       </c>
-      <c r="O99" s="7">
+      <c r="O99" s="6">
         <v>0.07169</v>
       </c>
-      <c r="P99" s="7">
+      <c r="P99" s="6">
         <v>0.072424</v>
       </c>
     </row>
@@ -6246,22 +6242,22 @@
       <c r="B100" s="6">
         <v>0.0740114</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="6">
         <v>0.0874973</v>
       </c>
-      <c r="D100" s="7">
+      <c r="D100" s="6">
         <v>0.089492</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="6">
         <v>0.089528</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F100" s="6">
         <v>0.082822</v>
       </c>
-      <c r="G100" s="7">
+      <c r="G100" s="6">
         <v>0.074692</v>
       </c>
-      <c r="H100" s="7">
+      <c r="H100" s="6">
         <v>0.074188</v>
       </c>
       <c r="I100" s="4">
@@ -6270,22 +6266,22 @@
       <c r="J100" s="6">
         <v>0.065653</v>
       </c>
-      <c r="K100" s="7">
+      <c r="K100" s="6">
         <v>0.0732844</v>
       </c>
-      <c r="L100" s="7">
+      <c r="L100" s="6">
         <v>0.074167</v>
       </c>
-      <c r="M100" s="7">
+      <c r="M100" s="6">
         <v>0.074582</v>
       </c>
-      <c r="N100" s="7">
+      <c r="N100" s="6">
         <v>0.072836</v>
       </c>
-      <c r="O100" s="7">
+      <c r="O100" s="6">
         <v>0.06757</v>
       </c>
-      <c r="P100" s="7">
+      <c r="P100" s="6">
         <v>0.066735</v>
       </c>
     </row>
@@ -6296,46 +6292,46 @@
       <c r="B101" s="6">
         <v>0.0692549</v>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="6">
         <v>0.0803013</v>
       </c>
-      <c r="D101" s="7">
+      <c r="D101" s="6">
         <v>0.078547</v>
       </c>
-      <c r="E101" s="7">
+      <c r="E101" s="6">
         <v>0.078543</v>
       </c>
-      <c r="F101" s="7">
+      <c r="F101" s="6">
         <v>0.077844</v>
       </c>
-      <c r="G101" s="7">
+      <c r="G101" s="6">
         <v>0.072785</v>
       </c>
-      <c r="H101" s="7">
+      <c r="H101" s="6">
         <v>0.07326</v>
       </c>
       <c r="I101" s="4">
         <v>64</v>
       </c>
-      <c r="J101" s="7">
+      <c r="J101" s="6">
         <v>0.0652368</v>
       </c>
-      <c r="K101" s="7">
+      <c r="K101" s="6">
         <v>0.0705998</v>
       </c>
-      <c r="L101" s="7">
+      <c r="L101" s="6">
         <v>0.07149</v>
       </c>
-      <c r="M101" s="7">
+      <c r="M101" s="6">
         <v>0.073551</v>
       </c>
-      <c r="N101" s="7">
+      <c r="N101" s="6">
         <v>0.072599</v>
       </c>
       <c r="O101" s="6">
         <v>0.064287</v>
       </c>
-      <c r="P101" s="7">
+      <c r="P101" s="6">
         <v>0.068456</v>
       </c>
     </row>
@@ -6346,40 +6342,40 @@
       <c r="B102" s="6">
         <v>0.0744673</v>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="6">
         <v>0.0852296</v>
       </c>
-      <c r="D102" s="7">
+      <c r="D102" s="6">
         <v>0.089718</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E102" s="6">
         <v>0.089745</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="6">
         <v>0.089889</v>
       </c>
-      <c r="G102" s="7">
+      <c r="G102" s="6">
         <v>0.075383</v>
       </c>
-      <c r="H102" s="7">
+      <c r="H102" s="6">
         <v>0.07482</v>
       </c>
       <c r="I102" s="4">
         <v>64</v>
       </c>
-      <c r="J102" s="7">
+      <c r="J102" s="6">
         <v>0.0698581</v>
       </c>
-      <c r="K102" s="7">
+      <c r="K102" s="6">
         <v>0.0747167</v>
       </c>
-      <c r="L102" s="7">
+      <c r="L102" s="6">
         <v>0.073232</v>
       </c>
-      <c r="M102" s="7">
+      <c r="M102" s="6">
         <v>0.073135</v>
       </c>
-      <c r="N102" s="7">
+      <c r="N102" s="6">
         <v>0.071977</v>
       </c>
       <c r="O102" s="6">
@@ -6396,40 +6392,40 @@
       <c r="B103" s="6">
         <v>0.0680358</v>
       </c>
-      <c r="C103" s="7">
+      <c r="C103" s="6">
         <v>0.0819451</v>
       </c>
-      <c r="D103" s="7">
+      <c r="D103" s="6">
         <v>0.082189</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E103" s="6">
         <v>0.082204</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="6">
         <v>0.075103</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G103" s="6">
         <v>0.070574</v>
       </c>
-      <c r="H103" s="7">
+      <c r="H103" s="6">
         <v>0.07044</v>
       </c>
       <c r="I103" s="4">
         <v>64</v>
       </c>
-      <c r="J103" s="7">
+      <c r="J103" s="6">
         <v>0.0669507</v>
       </c>
-      <c r="K103" s="7">
+      <c r="K103" s="6">
         <v>0.0720055</v>
       </c>
-      <c r="L103" s="7">
+      <c r="L103" s="6">
         <v>0.071675</v>
       </c>
-      <c r="M103" s="7">
+      <c r="M103" s="6">
         <v>0.06958</v>
       </c>
-      <c r="N103" s="7">
+      <c r="N103" s="6">
         <v>0.070903</v>
       </c>
       <c r="O103" s="6">
@@ -6443,19 +6439,19 @@
       <c r="A104" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="6">
         <v>0.0749115</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="6">
         <v>0.0882605</v>
       </c>
-      <c r="D104" s="7">
+      <c r="D104" s="6">
         <v>0.089006</v>
       </c>
-      <c r="E104" s="7">
+      <c r="E104" s="6">
         <v>0.089069</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="6">
         <v>0.088112</v>
       </c>
       <c r="G104" s="6">
@@ -6470,22 +6466,22 @@
       <c r="J104" s="6">
         <v>0.070575</v>
       </c>
-      <c r="K104" s="7">
+      <c r="K104" s="6">
         <v>0.0834203</v>
       </c>
-      <c r="L104" s="7">
+      <c r="L104" s="6">
         <v>0.078766</v>
       </c>
-      <c r="M104" s="7">
+      <c r="M104" s="6">
         <v>0.078931</v>
       </c>
-      <c r="N104" s="7">
+      <c r="N104" s="6">
         <v>0.079036</v>
       </c>
-      <c r="O104" s="7">
+      <c r="O104" s="6">
         <v>0.071084</v>
       </c>
-      <c r="P104" s="7">
+      <c r="P104" s="6">
         <v>0.074457</v>
       </c>
     </row>
@@ -6493,19 +6489,19 @@
       <c r="A105" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="6">
         <v>0.0741051</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="6">
         <v>0.084899</v>
       </c>
-      <c r="D105" s="7">
+      <c r="D105" s="6">
         <v>0.084752</v>
       </c>
-      <c r="E105" s="7">
+      <c r="E105" s="6">
         <v>0.084756</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="6">
         <v>0.083957</v>
       </c>
       <c r="G105" s="6">
@@ -6517,19 +6513,19 @@
       <c r="I105" s="4">
         <v>64</v>
       </c>
-      <c r="J105" s="7">
+      <c r="J105" s="6">
         <v>0.0690255</v>
       </c>
-      <c r="K105" s="7">
+      <c r="K105" s="6">
         <v>0.0728244</v>
       </c>
-      <c r="L105" s="7">
+      <c r="L105" s="6">
         <v>0.073531</v>
       </c>
-      <c r="M105" s="7">
+      <c r="M105" s="6">
         <v>0.073582</v>
       </c>
-      <c r="N105" s="7">
+      <c r="N105" s="6">
         <v>0.071296</v>
       </c>
       <c r="O105" s="6">
@@ -6540,40 +6536,40 @@
       </c>
     </row>
     <row r="106" spans="1:16">
-      <c r="A106" s="8"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="7"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="9"/>
-      <c r="M106" s="9"/>
-      <c r="N106" s="9"/>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
+      <c r="A106" s="7"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="N106" s="8"/>
+      <c r="O106" s="8"/>
+      <c r="P106" s="8"/>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="6">
         <v>0.0619579</v>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="6">
         <v>0.0697182</v>
       </c>
-      <c r="D107" s="7">
+      <c r="D107" s="6">
         <v>0.07624</v>
       </c>
-      <c r="E107" s="7">
+      <c r="E107" s="6">
         <v>0.076474</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="6">
         <v>0.070412</v>
       </c>
       <c r="G107" s="6">
@@ -6585,22 +6581,22 @@
       <c r="I107" s="4">
         <v>8</v>
       </c>
-      <c r="J107" s="7">
+      <c r="J107" s="6">
         <v>0.0452129</v>
       </c>
-      <c r="K107" s="7">
+      <c r="K107" s="6">
         <v>0.0511419</v>
       </c>
-      <c r="L107" s="7">
+      <c r="L107" s="6">
         <v>0.04959</v>
       </c>
-      <c r="M107" s="7">
+      <c r="M107" s="6">
         <v>0.049095</v>
       </c>
       <c r="N107" s="6">
         <v>0.041376</v>
       </c>
-      <c r="O107" s="7">
+      <c r="O107" s="6">
         <v>0.045365</v>
       </c>
       <c r="P107" s="6">
@@ -6611,22 +6607,22 @@
       <c r="A108" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="6">
         <v>0.0616848</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="6">
         <v>0.0786405</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D108" s="6">
         <v>0.080863</v>
       </c>
-      <c r="E108" s="7">
+      <c r="E108" s="6">
         <v>0.080723</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="6">
         <v>0.068197</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G108" s="6">
         <v>0.061243</v>
       </c>
       <c r="H108" s="6">
@@ -6638,22 +6634,22 @@
       <c r="J108" s="6">
         <v>0.0420188</v>
       </c>
-      <c r="K108" s="7">
+      <c r="K108" s="6">
         <v>0.0494114</v>
       </c>
-      <c r="L108" s="7">
+      <c r="L108" s="6">
         <v>0.05033</v>
       </c>
-      <c r="M108" s="7">
+      <c r="M108" s="6">
         <v>0.051363</v>
       </c>
-      <c r="N108" s="7">
+      <c r="N108" s="6">
         <v>0.046284</v>
       </c>
-      <c r="O108" s="7">
+      <c r="O108" s="6">
         <v>0.05058</v>
       </c>
-      <c r="P108" s="7">
+      <c r="P108" s="6">
         <v>0.051128</v>
       </c>
     </row>
@@ -6661,19 +6657,19 @@
       <c r="A109" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="6">
         <v>0.0613074</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="6">
         <v>0.0700287</v>
       </c>
-      <c r="D109" s="7">
+      <c r="D109" s="6">
         <v>0.080208</v>
       </c>
-      <c r="E109" s="7">
+      <c r="E109" s="6">
         <v>0.079993</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="6">
         <v>0.066003</v>
       </c>
       <c r="G109" s="6">
@@ -6685,25 +6681,25 @@
       <c r="I109" s="4">
         <v>8</v>
       </c>
-      <c r="J109" s="7">
+      <c r="J109" s="6">
         <v>0.044675</v>
       </c>
-      <c r="K109" s="7">
+      <c r="K109" s="6">
         <v>0.0497733</v>
       </c>
-      <c r="L109" s="7">
+      <c r="L109" s="6">
         <v>0.045822</v>
       </c>
-      <c r="M109" s="7">
+      <c r="M109" s="6">
         <v>0.045511</v>
       </c>
       <c r="N109" s="6">
         <v>0.04319</v>
       </c>
-      <c r="O109" s="7">
+      <c r="O109" s="6">
         <v>0.048291</v>
       </c>
-      <c r="P109" s="7">
+      <c r="P109" s="6">
         <v>0.046645</v>
       </c>
     </row>
@@ -6714,46 +6710,46 @@
       <c r="B110" s="6">
         <v>0.0585942</v>
       </c>
-      <c r="C110" s="7">
+      <c r="C110" s="6">
         <v>0.0761087</v>
       </c>
-      <c r="D110" s="7">
+      <c r="D110" s="6">
         <v>0.075542</v>
       </c>
-      <c r="E110" s="7">
+      <c r="E110" s="6">
         <v>0.074261</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F110" s="6">
         <v>0.064629</v>
       </c>
-      <c r="G110" s="7">
+      <c r="G110" s="6">
         <v>0.06032</v>
       </c>
-      <c r="H110" s="7">
+      <c r="H110" s="6">
         <v>0.060135</v>
       </c>
       <c r="I110" s="4">
         <v>8</v>
       </c>
-      <c r="J110" s="7">
+      <c r="J110" s="6">
         <v>0.0450346</v>
       </c>
       <c r="K110" s="6">
         <v>0.0438599</v>
       </c>
-      <c r="L110" s="7">
+      <c r="L110" s="6">
         <v>0.044278</v>
       </c>
-      <c r="M110" s="7">
+      <c r="M110" s="6">
         <v>0.045854</v>
       </c>
-      <c r="N110" s="7">
+      <c r="N110" s="6">
         <v>0.045394</v>
       </c>
-      <c r="O110" s="7">
+      <c r="O110" s="6">
         <v>0.04546</v>
       </c>
-      <c r="P110" s="7">
+      <c r="P110" s="6">
         <v>0.04772</v>
       </c>
     </row>
@@ -6761,25 +6757,25 @@
       <c r="A111" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="6">
         <v>0.0592219</v>
       </c>
-      <c r="C111" s="7">
+      <c r="C111" s="6">
         <v>0.0780361</v>
       </c>
-      <c r="D111" s="7">
+      <c r="D111" s="6">
         <v>0.079752</v>
       </c>
-      <c r="E111" s="7">
+      <c r="E111" s="6">
         <v>0.078699</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="6">
         <v>0.06667</v>
       </c>
       <c r="G111" s="6">
         <v>0.057118</v>
       </c>
-      <c r="H111" s="7">
+      <c r="H111" s="6">
         <v>0.061274</v>
       </c>
       <c r="I111" s="4">
@@ -6788,22 +6784,22 @@
       <c r="J111" s="6">
         <v>0.0429519</v>
       </c>
-      <c r="K111" s="7">
+      <c r="K111" s="6">
         <v>0.0485673</v>
       </c>
-      <c r="L111" s="7">
+      <c r="L111" s="6">
         <v>0.047503</v>
       </c>
-      <c r="M111" s="7">
+      <c r="M111" s="6">
         <v>0.047195</v>
       </c>
-      <c r="N111" s="7">
+      <c r="N111" s="6">
         <v>0.043291</v>
       </c>
-      <c r="O111" s="7">
+      <c r="O111" s="6">
         <v>0.046125</v>
       </c>
-      <c r="P111" s="7">
+      <c r="P111" s="6">
         <v>0.045754</v>
       </c>
     </row>
@@ -6811,22 +6807,22 @@
       <c r="A112" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="6">
         <v>0.0519548</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="6">
         <v>0.0651943</v>
       </c>
-      <c r="D112" s="7">
+      <c r="D112" s="6">
         <v>0.064955</v>
       </c>
-      <c r="E112" s="7">
+      <c r="E112" s="6">
         <v>0.068375</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="6">
         <v>0.060955</v>
       </c>
-      <c r="G112" s="7">
+      <c r="G112" s="6">
         <v>0.052102</v>
       </c>
       <c r="H112" s="6">
@@ -6835,10 +6831,10 @@
       <c r="I112" s="4">
         <v>16</v>
       </c>
-      <c r="J112" s="7">
+      <c r="J112" s="6">
         <v>0.0448449</v>
       </c>
-      <c r="K112" s="7">
+      <c r="K112" s="6">
         <v>0.0465877</v>
       </c>
       <c r="L112" s="6">
@@ -6853,7 +6849,7 @@
       <c r="O112" s="6">
         <v>0.042158</v>
       </c>
-      <c r="P112" s="7">
+      <c r="P112" s="6">
         <v>0.044872</v>
       </c>
     </row>
@@ -6861,34 +6857,34 @@
       <c r="A113" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="6">
         <v>0.0515357</v>
       </c>
-      <c r="C113" s="7">
+      <c r="C113" s="6">
         <v>0.0640009</v>
       </c>
-      <c r="D113" s="7">
+      <c r="D113" s="6">
         <v>0.064717</v>
       </c>
-      <c r="E113" s="7">
+      <c r="E113" s="6">
         <v>0.066652</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="6">
         <v>0.057673</v>
       </c>
       <c r="G113" s="6">
         <v>0.051526</v>
       </c>
-      <c r="H113" s="7">
+      <c r="H113" s="6">
         <v>0.052386</v>
       </c>
       <c r="I113" s="4">
         <v>16</v>
       </c>
-      <c r="J113" s="7">
+      <c r="J113" s="6">
         <v>0.0487074</v>
       </c>
-      <c r="K113" s="7">
+      <c r="K113" s="6">
         <v>0.0460363</v>
       </c>
       <c r="L113" s="6">
@@ -6914,34 +6910,34 @@
       <c r="B114" s="6">
         <v>0.0495026</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="6">
         <v>0.0643139</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D114" s="6">
         <v>0.067487</v>
       </c>
-      <c r="E114" s="7">
+      <c r="E114" s="6">
         <v>0.06493</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="6">
         <v>0.057766</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G114" s="6">
         <v>0.050501</v>
       </c>
-      <c r="H114" s="7">
+      <c r="H114" s="6">
         <v>0.050291</v>
       </c>
       <c r="I114" s="4">
         <v>16</v>
       </c>
-      <c r="J114" s="7">
+      <c r="J114" s="6">
         <v>0.045313</v>
       </c>
-      <c r="K114" s="7">
+      <c r="K114" s="6">
         <v>0.0435058</v>
       </c>
-      <c r="L114" s="7">
+      <c r="L114" s="6">
         <v>0.043853</v>
       </c>
       <c r="M114" s="6">
@@ -6964,37 +6960,37 @@
       <c r="B115" s="6">
         <v>0.0523381</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="6">
         <v>0.0627612</v>
       </c>
-      <c r="D115" s="7">
+      <c r="D115" s="6">
         <v>0.067238</v>
       </c>
-      <c r="E115" s="7">
+      <c r="E115" s="6">
         <v>0.06762</v>
       </c>
-      <c r="F115" s="7">
+      <c r="F115" s="6">
         <v>0.059407</v>
       </c>
-      <c r="G115" s="7">
+      <c r="G115" s="6">
         <v>0.054498</v>
       </c>
-      <c r="H115" s="7">
+      <c r="H115" s="6">
         <v>0.053223</v>
       </c>
       <c r="I115" s="4">
         <v>16</v>
       </c>
-      <c r="J115" s="7">
+      <c r="J115" s="6">
         <v>0.044986</v>
       </c>
-      <c r="K115" s="7">
+      <c r="K115" s="6">
         <v>0.0431814</v>
       </c>
-      <c r="L115" s="7">
+      <c r="L115" s="6">
         <v>0.044311</v>
       </c>
-      <c r="M115" s="7">
+      <c r="M115" s="6">
         <v>0.044066</v>
       </c>
       <c r="N115" s="6">
@@ -7011,37 +7007,37 @@
       <c r="A116" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="6">
         <v>0.0497995</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="6">
         <v>0.0664164</v>
       </c>
-      <c r="D116" s="7">
+      <c r="D116" s="6">
         <v>0.066713</v>
       </c>
-      <c r="E116" s="7">
+      <c r="E116" s="6">
         <v>0.06577</v>
       </c>
-      <c r="F116" s="7">
+      <c r="F116" s="6">
         <v>0.059721</v>
       </c>
       <c r="G116" s="6">
         <v>0.049368</v>
       </c>
-      <c r="H116" s="7">
+      <c r="H116" s="6">
         <v>0.051931</v>
       </c>
       <c r="I116" s="4">
         <v>16</v>
       </c>
-      <c r="J116" s="7">
+      <c r="J116" s="6">
         <v>0.0463508</v>
       </c>
-      <c r="K116" s="7">
+      <c r="K116" s="6">
         <v>0.0444398</v>
       </c>
-      <c r="L116" s="7">
+      <c r="L116" s="6">
         <v>0.044951</v>
       </c>
       <c r="M116" s="6">
@@ -7061,19 +7057,19 @@
       <c r="A117" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="6">
         <v>0.0495477</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="6">
         <v>0.0636354</v>
       </c>
-      <c r="D117" s="7">
+      <c r="D117" s="6">
         <v>0.061283</v>
       </c>
-      <c r="E117" s="7">
+      <c r="E117" s="6">
         <v>0.061144</v>
       </c>
-      <c r="F117" s="7">
+      <c r="F117" s="6">
         <v>0.057001</v>
       </c>
       <c r="G117" s="6">
@@ -7085,25 +7081,25 @@
       <c r="I117" s="4">
         <v>32</v>
       </c>
-      <c r="J117" s="7">
+      <c r="J117" s="6">
         <v>0.0406101</v>
       </c>
-      <c r="K117" s="7">
+      <c r="K117" s="6">
         <v>0.041694</v>
       </c>
-      <c r="L117" s="7">
+      <c r="L117" s="6">
         <v>0.043046</v>
       </c>
-      <c r="M117" s="7">
+      <c r="M117" s="6">
         <v>0.043864</v>
       </c>
       <c r="N117" s="6">
         <v>0.040112</v>
       </c>
-      <c r="O117" s="7">
+      <c r="O117" s="6">
         <v>0.042782</v>
       </c>
-      <c r="P117" s="7">
+      <c r="P117" s="6">
         <v>0.043572</v>
       </c>
     </row>
@@ -7111,19 +7107,19 @@
       <c r="A118" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="6">
         <v>0.0476473</v>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="6">
         <v>0.0622174</v>
       </c>
-      <c r="D118" s="7">
+      <c r="D118" s="6">
         <v>0.060459</v>
       </c>
-      <c r="E118" s="7">
+      <c r="E118" s="6">
         <v>0.06052</v>
       </c>
-      <c r="F118" s="7">
+      <c r="F118" s="6">
         <v>0.056411</v>
       </c>
       <c r="G118" s="6">
@@ -7135,25 +7131,25 @@
       <c r="I118" s="4">
         <v>32</v>
       </c>
-      <c r="J118" s="7">
+      <c r="J118" s="6">
         <v>0.0413478</v>
       </c>
-      <c r="K118" s="7">
+      <c r="K118" s="6">
         <v>0.0447781</v>
       </c>
-      <c r="L118" s="7">
+      <c r="L118" s="6">
         <v>0.041594</v>
       </c>
-      <c r="M118" s="7">
+      <c r="M118" s="6">
         <v>0.041693</v>
       </c>
       <c r="N118" s="6">
         <v>0.040722</v>
       </c>
-      <c r="O118" s="7">
+      <c r="O118" s="6">
         <v>0.043821</v>
       </c>
-      <c r="P118" s="7">
+      <c r="P118" s="6">
         <v>0.043286</v>
       </c>
     </row>
@@ -7161,34 +7157,34 @@
       <c r="A119" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="6">
         <v>0.0466152</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="6">
         <v>0.060314</v>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="6">
         <v>0.06049</v>
       </c>
-      <c r="E119" s="7">
+      <c r="E119" s="6">
         <v>0.062709</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F119" s="6">
         <v>0.055633</v>
       </c>
       <c r="G119" s="6">
         <v>0.0459</v>
       </c>
-      <c r="H119" s="7">
+      <c r="H119" s="6">
         <v>0.048246</v>
       </c>
       <c r="I119" s="4">
         <v>32</v>
       </c>
-      <c r="J119" s="7">
+      <c r="J119" s="6">
         <v>0.0405106</v>
       </c>
-      <c r="K119" s="7">
+      <c r="K119" s="6">
         <v>0.0406564</v>
       </c>
       <c r="L119" s="6">
@@ -7200,10 +7196,10 @@
       <c r="N119" s="6">
         <v>0.04023</v>
       </c>
-      <c r="O119" s="7">
+      <c r="O119" s="6">
         <v>0.04522</v>
       </c>
-      <c r="P119" s="7">
+      <c r="P119" s="6">
         <v>0.04259</v>
       </c>
     </row>
@@ -7214,22 +7210,22 @@
       <c r="B120" s="6">
         <v>0.0464304</v>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="6">
         <v>0.060474</v>
       </c>
-      <c r="D120" s="7">
+      <c r="D120" s="6">
         <v>0.062975</v>
       </c>
-      <c r="E120" s="7">
+      <c r="E120" s="6">
         <v>0.06288</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F120" s="6">
         <v>0.055305</v>
       </c>
-      <c r="G120" s="7">
+      <c r="G120" s="6">
         <v>0.046653</v>
       </c>
-      <c r="H120" s="7">
+      <c r="H120" s="6">
         <v>0.047809</v>
       </c>
       <c r="I120" s="4">
@@ -7238,22 +7234,22 @@
       <c r="J120" s="6">
         <v>0.0385797</v>
       </c>
-      <c r="K120" s="7">
+      <c r="K120" s="6">
         <v>0.0392822</v>
       </c>
-      <c r="L120" s="7">
+      <c r="L120" s="6">
         <v>0.040359</v>
       </c>
-      <c r="M120" s="7">
+      <c r="M120" s="6">
         <v>0.041447</v>
       </c>
-      <c r="N120" s="7">
+      <c r="N120" s="6">
         <v>0.040596</v>
       </c>
-      <c r="O120" s="7">
+      <c r="O120" s="6">
         <v>0.04114</v>
       </c>
-      <c r="P120" s="7">
+      <c r="P120" s="6">
         <v>0.042887</v>
       </c>
     </row>
@@ -7261,19 +7257,19 @@
       <c r="A121" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="6">
         <v>0.0474678</v>
       </c>
-      <c r="C121" s="7">
+      <c r="C121" s="6">
         <v>0.0585333</v>
       </c>
-      <c r="D121" s="7">
+      <c r="D121" s="6">
         <v>0.060901</v>
       </c>
-      <c r="E121" s="7">
+      <c r="E121" s="6">
         <v>0.060723</v>
       </c>
-      <c r="F121" s="7">
+      <c r="F121" s="6">
         <v>0.054594</v>
       </c>
       <c r="G121" s="6">
@@ -7285,25 +7281,25 @@
       <c r="I121" s="4">
         <v>32</v>
       </c>
-      <c r="J121" s="7">
+      <c r="J121" s="6">
         <v>0.0407326</v>
       </c>
-      <c r="K121" s="7">
+      <c r="K121" s="6">
         <v>0.0400416</v>
       </c>
       <c r="L121" s="6">
         <v>0.039907</v>
       </c>
-      <c r="M121" s="7">
+      <c r="M121" s="6">
         <v>0.041241</v>
       </c>
-      <c r="N121" s="7">
+      <c r="N121" s="6">
         <v>0.040777</v>
       </c>
-      <c r="O121" s="7">
+      <c r="O121" s="6">
         <v>0.040908</v>
       </c>
-      <c r="P121" s="7">
+      <c r="P121" s="6">
         <v>0.043616</v>
       </c>
     </row>
@@ -7311,49 +7307,49 @@
       <c r="A122" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="6">
         <v>0.047912</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="6">
         <v>0.0588426</v>
       </c>
-      <c r="D122" s="7">
+      <c r="D122" s="6">
         <v>0.055878</v>
       </c>
-      <c r="E122" s="7">
+      <c r="E122" s="6">
         <v>0.055882</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="6">
         <v>0.056017</v>
       </c>
       <c r="G122" s="6">
         <v>0.047317</v>
       </c>
-      <c r="H122" s="7">
+      <c r="H122" s="6">
         <v>0.048955</v>
       </c>
       <c r="I122" s="4">
         <v>64</v>
       </c>
-      <c r="J122" s="7">
+      <c r="J122" s="6">
         <v>0.0399684</v>
       </c>
       <c r="K122" s="6">
         <v>0.0387548</v>
       </c>
-      <c r="L122" s="7">
+      <c r="L122" s="6">
         <v>0.040508</v>
       </c>
-      <c r="M122" s="7">
+      <c r="M122" s="6">
         <v>0.03878</v>
       </c>
-      <c r="N122" s="7">
+      <c r="N122" s="6">
         <v>0.039675</v>
       </c>
-      <c r="O122" s="7">
+      <c r="O122" s="6">
         <v>0.039903</v>
       </c>
-      <c r="P122" s="7">
+      <c r="P122" s="6">
         <v>0.040425</v>
       </c>
     </row>
@@ -7361,19 +7357,19 @@
       <c r="A123" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="6">
         <v>0.0478618</v>
       </c>
-      <c r="C123" s="7">
+      <c r="C123" s="6">
         <v>0.0568092</v>
       </c>
-      <c r="D123" s="7">
+      <c r="D123" s="6">
         <v>0.057966</v>
       </c>
-      <c r="E123" s="7">
+      <c r="E123" s="6">
         <v>0.05816</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="6">
         <v>0.0554</v>
       </c>
       <c r="G123" s="6">
@@ -7385,25 +7381,25 @@
       <c r="I123" s="4">
         <v>64</v>
       </c>
-      <c r="J123" s="7">
+      <c r="J123" s="6">
         <v>0.0406812</v>
       </c>
-      <c r="K123" s="7">
+      <c r="K123" s="6">
         <v>0.0416469</v>
       </c>
-      <c r="L123" s="7">
+      <c r="L123" s="6">
         <v>0.041426</v>
       </c>
-      <c r="M123" s="7">
+      <c r="M123" s="6">
         <v>0.041523</v>
       </c>
       <c r="N123" s="6">
         <v>0.040524</v>
       </c>
-      <c r="O123" s="7">
+      <c r="O123" s="6">
         <v>0.043642</v>
       </c>
-      <c r="P123" s="7">
+      <c r="P123" s="6">
         <v>0.042195</v>
       </c>
     </row>
@@ -7411,19 +7407,19 @@
       <c r="A124" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="6">
         <v>0.0452311</v>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="6">
         <v>0.0580158</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D124" s="6">
         <v>0.058279</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E124" s="6">
         <v>0.058351</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="6">
         <v>0.055318</v>
       </c>
       <c r="G124" s="6">
@@ -7435,25 +7431,25 @@
       <c r="I124" s="4">
         <v>64</v>
       </c>
-      <c r="J124" s="7">
+      <c r="J124" s="6">
         <v>0.0398835</v>
       </c>
-      <c r="K124" s="7">
+      <c r="K124" s="6">
         <v>0.0394978</v>
       </c>
-      <c r="L124" s="7">
+      <c r="L124" s="6">
         <v>0.040292</v>
       </c>
       <c r="M124" s="6">
         <v>0.039495</v>
       </c>
-      <c r="N124" s="7">
+      <c r="N124" s="6">
         <v>0.041358</v>
       </c>
-      <c r="O124" s="7">
+      <c r="O124" s="6">
         <v>0.040184</v>
       </c>
-      <c r="P124" s="7">
+      <c r="P124" s="6">
         <v>0.043347</v>
       </c>
     </row>
@@ -7461,49 +7457,49 @@
       <c r="A125" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="6">
         <v>0.0453769</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="6">
         <v>0.0559333</v>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="6">
         <v>0.056556</v>
       </c>
-      <c r="E125" s="7">
+      <c r="E125" s="6">
         <v>0.056528</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="6">
         <v>0.054414</v>
       </c>
       <c r="G125" s="6">
         <v>0.044134</v>
       </c>
-      <c r="H125" s="7">
+      <c r="H125" s="6">
         <v>0.046361</v>
       </c>
       <c r="I125" s="4">
         <v>64</v>
       </c>
-      <c r="J125" s="7">
+      <c r="J125" s="6">
         <v>0.0396804</v>
       </c>
-      <c r="K125" s="7">
+      <c r="K125" s="6">
         <v>0.0399038</v>
       </c>
       <c r="L125" s="6">
         <v>0.038796</v>
       </c>
-      <c r="M125" s="7">
+      <c r="M125" s="6">
         <v>0.040639</v>
       </c>
-      <c r="N125" s="7">
+      <c r="N125" s="6">
         <v>0.042381</v>
       </c>
-      <c r="O125" s="7">
+      <c r="O125" s="6">
         <v>0.041787</v>
       </c>
-      <c r="P125" s="7">
+      <c r="P125" s="6">
         <v>0.042555</v>
       </c>
     </row>
@@ -7511,19 +7507,19 @@
       <c r="A126" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="6">
         <v>0.0457404</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="6">
         <v>0.0576394</v>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="6">
         <v>0.056371</v>
       </c>
-      <c r="E126" s="7">
+      <c r="E126" s="6">
         <v>0.056378</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F126" s="6">
         <v>0.053453</v>
       </c>
       <c r="G126" s="6">
@@ -7538,899 +7534,1099 @@
       <c r="J126" s="6">
         <v>0.0385955</v>
       </c>
-      <c r="K126" s="7">
+      <c r="K126" s="6">
         <v>0.0401385</v>
       </c>
-      <c r="L126" s="7">
+      <c r="L126" s="6">
         <v>0.039083</v>
       </c>
-      <c r="M126" s="7">
+      <c r="M126" s="6">
         <v>0.038744</v>
       </c>
-      <c r="N126" s="7">
+      <c r="N126" s="6">
         <v>0.039551</v>
       </c>
-      <c r="O126" s="7">
+      <c r="O126" s="6">
         <v>0.042261</v>
       </c>
-      <c r="P126" s="7">
+      <c r="P126" s="6">
         <v>0.042795</v>
       </c>
     </row>
     <row r="127" spans="1:16">
-      <c r="A127" s="8"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="9"/>
-      <c r="M127" s="9"/>
-      <c r="N127" s="9"/>
-      <c r="O127" s="9"/>
-      <c r="P127" s="9"/>
+      <c r="A127" s="7"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
+      <c r="N127" s="8"/>
+      <c r="O127" s="8"/>
+      <c r="P127" s="8"/>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="6">
         <v>0.354079</v>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="6">
         <v>0.342444</v>
       </c>
-      <c r="D128" s="7">
-        <v>0</v>
-      </c>
-      <c r="E128" s="7">
-        <v>0</v>
-      </c>
-      <c r="F128" s="7">
+      <c r="D128" s="6">
+        <v>0.334842</v>
+      </c>
+      <c r="E128" s="6">
+        <v>0.337589</v>
+      </c>
+      <c r="F128" s="6">
         <v>0.358425</v>
       </c>
-      <c r="G128" s="7">
-        <v>0</v>
-      </c>
-      <c r="H128" s="7">
+      <c r="G128" s="6">
+        <v>0.325745</v>
+      </c>
+      <c r="H128" s="6">
         <v>0.340338</v>
       </c>
       <c r="I128" s="4">
         <v>8</v>
       </c>
-      <c r="J128" s="7">
+      <c r="J128" s="6">
         <v>0.286505</v>
       </c>
-      <c r="K128" s="7">
+      <c r="K128" s="6">
         <v>0.259106</v>
       </c>
-      <c r="L128" s="9"/>
-      <c r="M128" s="9"/>
-      <c r="N128" s="9"/>
-      <c r="O128" s="9"/>
-      <c r="P128" s="9"/>
+      <c r="L128" s="6">
+        <v>0.224183</v>
+      </c>
+      <c r="M128" s="6">
+        <v>0.259037</v>
+      </c>
+      <c r="N128" s="6">
+        <v>0.237489</v>
+      </c>
+      <c r="O128" s="6">
+        <v>0.245821</v>
+      </c>
+      <c r="P128" s="6">
+        <v>0.273534</v>
+      </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="6">
         <v>0.352279</v>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="6">
         <v>0.341732</v>
       </c>
-      <c r="D129" s="7">
-        <v>0</v>
-      </c>
-      <c r="E129" s="7">
+      <c r="D129" s="6">
+        <v>0.329489</v>
+      </c>
+      <c r="E129" s="6">
         <v>0.364894</v>
       </c>
-      <c r="F129" s="7">
-        <v>0</v>
-      </c>
-      <c r="G129" s="7">
-        <v>0</v>
-      </c>
-      <c r="H129" s="7">
-        <v>0</v>
+      <c r="F129" s="6">
+        <v>0.342469</v>
+      </c>
+      <c r="G129" s="6">
+        <v>0.346668</v>
+      </c>
+      <c r="H129" s="6">
+        <v>0.335786</v>
       </c>
       <c r="I129" s="4">
         <v>8</v>
       </c>
-      <c r="J129" s="7">
+      <c r="J129" s="6">
         <v>0.284734</v>
       </c>
-      <c r="K129" s="7">
+      <c r="K129" s="6">
         <v>0.266364</v>
       </c>
-      <c r="L129" s="9"/>
-      <c r="M129" s="9"/>
-      <c r="N129" s="9"/>
-      <c r="O129" s="9"/>
-      <c r="P129" s="9"/>
+      <c r="L129" s="6">
+        <v>0.259536</v>
+      </c>
+      <c r="M129" s="6">
+        <v>0.269</v>
+      </c>
+      <c r="N129" s="6">
+        <v>0.256314</v>
+      </c>
+      <c r="O129" s="6">
+        <v>0.260494</v>
+      </c>
+      <c r="P129" s="6">
+        <v>0.281656</v>
+      </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="6">
         <v>0.344691</v>
       </c>
-      <c r="C130" s="7">
+      <c r="C130" s="6">
         <v>0.362231</v>
       </c>
-      <c r="D130" s="7">
-        <v>0</v>
-      </c>
-      <c r="E130" s="7">
-        <v>0</v>
-      </c>
-      <c r="F130" s="7">
-        <v>0</v>
-      </c>
-      <c r="G130" s="7">
-        <v>0</v>
-      </c>
-      <c r="H130" s="7">
-        <v>0</v>
+      <c r="D130" s="6">
+        <v>0.341962</v>
+      </c>
+      <c r="E130" s="6">
+        <v>0.333762</v>
+      </c>
+      <c r="F130" s="6">
+        <v>0.354538</v>
+      </c>
+      <c r="G130" s="6">
+        <v>0.305025</v>
+      </c>
+      <c r="H130" s="6">
+        <v>0.326497</v>
       </c>
       <c r="I130" s="4">
         <v>8</v>
       </c>
-      <c r="J130" s="7">
+      <c r="J130" s="6">
         <v>0.279559</v>
       </c>
-      <c r="K130" s="7">
+      <c r="K130" s="6">
         <v>0.261081</v>
       </c>
-      <c r="L130" s="9"/>
-      <c r="M130" s="9"/>
-      <c r="N130" s="9"/>
-      <c r="O130" s="9"/>
-      <c r="P130" s="9"/>
+      <c r="L130" s="6">
+        <v>0.254023</v>
+      </c>
+      <c r="M130" s="6">
+        <v>0.237876</v>
+      </c>
+      <c r="N130" s="6">
+        <v>0.238829</v>
+      </c>
+      <c r="O130" s="6">
+        <v>0.251658</v>
+      </c>
+      <c r="P130" s="6">
+        <v>0.26663</v>
+      </c>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="6">
         <v>0.339711</v>
       </c>
-      <c r="C131" s="7">
+      <c r="C131" s="6">
         <v>0.380713</v>
       </c>
-      <c r="D131" s="7">
-        <v>0</v>
-      </c>
-      <c r="E131" s="7">
-        <v>0</v>
-      </c>
-      <c r="F131" s="7">
-        <v>0</v>
-      </c>
-      <c r="G131" s="7">
-        <v>0</v>
-      </c>
-      <c r="H131" s="7">
-        <v>0</v>
+      <c r="D131" s="6">
+        <v>0.322678</v>
+      </c>
+      <c r="E131" s="6">
+        <v>0.34535</v>
+      </c>
+      <c r="F131" s="6">
+        <v>0.326917</v>
+      </c>
+      <c r="G131" s="6">
+        <v>0.316661</v>
+      </c>
+      <c r="H131" s="6">
+        <v>0.329173</v>
       </c>
       <c r="I131" s="4">
         <v>8</v>
       </c>
-      <c r="J131" s="7">
+      <c r="J131" s="6">
         <v>0.272972</v>
       </c>
-      <c r="K131" s="7">
+      <c r="K131" s="6">
         <v>0.275422</v>
       </c>
-      <c r="L131" s="9"/>
-      <c r="M131" s="9"/>
-      <c r="N131" s="9"/>
-      <c r="O131" s="9"/>
-      <c r="P131" s="9"/>
+      <c r="L131" s="6">
+        <v>0.262241</v>
+      </c>
+      <c r="M131" s="6">
+        <v>0.26802</v>
+      </c>
+      <c r="N131" s="6">
+        <v>0.257116</v>
+      </c>
+      <c r="O131" s="6">
+        <v>0.242204</v>
+      </c>
+      <c r="P131" s="6">
+        <v>0.255795</v>
+      </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="6">
         <v>0.331529</v>
       </c>
-      <c r="C132" s="7">
+      <c r="C132" s="6">
         <v>0.340709</v>
       </c>
-      <c r="D132" s="7">
-        <v>0</v>
-      </c>
-      <c r="E132" s="7">
-        <v>0</v>
-      </c>
-      <c r="F132" s="7">
-        <v>0</v>
-      </c>
-      <c r="G132" s="7">
-        <v>0</v>
-      </c>
-      <c r="H132" s="7">
-        <v>0</v>
+      <c r="D132" s="6">
+        <v>0.332016</v>
+      </c>
+      <c r="E132" s="6">
+        <v>0.331315</v>
+      </c>
+      <c r="F132" s="6">
+        <v>0.335605</v>
+      </c>
+      <c r="G132" s="6">
+        <v>0.335021</v>
+      </c>
+      <c r="H132" s="6">
+        <v>0.360178</v>
       </c>
       <c r="I132" s="4">
         <v>8</v>
       </c>
-      <c r="J132" s="7">
+      <c r="J132" s="6">
         <v>0.290377</v>
       </c>
-      <c r="K132" s="7">
+      <c r="K132" s="6">
         <v>0.272553</v>
       </c>
-      <c r="L132" s="9"/>
-      <c r="M132" s="9"/>
-      <c r="N132" s="9"/>
-      <c r="O132" s="9"/>
-      <c r="P132" s="9"/>
+      <c r="L132" s="6">
+        <v>0.268627</v>
+      </c>
+      <c r="M132" s="6">
+        <v>0.27796</v>
+      </c>
+      <c r="N132" s="6">
+        <v>0.254243</v>
+      </c>
+      <c r="O132" s="6">
+        <v>0.263004</v>
+      </c>
+      <c r="P132" s="6">
+        <v>0.288554</v>
+      </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="6">
         <v>0.302871</v>
       </c>
-      <c r="C133" s="7">
+      <c r="C133" s="6">
         <v>0.302298</v>
       </c>
-      <c r="D133" s="7">
+      <c r="D133" s="6">
         <v>0.313612</v>
       </c>
-      <c r="E133" s="7">
+      <c r="E133" s="6">
         <v>0.317064</v>
       </c>
-      <c r="F133" s="7">
+      <c r="F133" s="6">
         <v>0.302909</v>
       </c>
-      <c r="G133" s="7">
-        <v>0</v>
-      </c>
-      <c r="H133" s="7">
+      <c r="G133" s="6">
+        <v>0.27519</v>
+      </c>
+      <c r="H133" s="6">
         <v>0.295169</v>
       </c>
       <c r="I133" s="4">
         <v>16</v>
       </c>
-      <c r="J133" s="7">
+      <c r="J133" s="6">
         <v>0.278108</v>
       </c>
-      <c r="K133" s="7">
+      <c r="K133" s="6">
         <v>0.258878</v>
       </c>
-      <c r="L133" s="9"/>
-      <c r="M133" s="9"/>
-      <c r="N133" s="9"/>
-      <c r="O133" s="9"/>
-      <c r="P133" s="9"/>
+      <c r="L133" s="6">
+        <v>0.257114</v>
+      </c>
+      <c r="M133" s="6">
+        <v>0.26349</v>
+      </c>
+      <c r="N133" s="6">
+        <v>0.253942</v>
+      </c>
+      <c r="O133" s="6">
+        <v>0.263124</v>
+      </c>
+      <c r="P133" s="6">
+        <v>0.280784</v>
+      </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="6">
         <v>0.287204</v>
       </c>
-      <c r="C134" s="7">
+      <c r="C134" s="6">
         <v>0.299163</v>
       </c>
-      <c r="D134" s="7">
-        <v>0</v>
-      </c>
-      <c r="E134" s="7">
-        <v>0</v>
-      </c>
-      <c r="F134" s="7">
-        <v>0</v>
-      </c>
-      <c r="G134" s="7">
-        <v>0</v>
-      </c>
-      <c r="H134" s="7">
-        <v>0</v>
+      <c r="D134" s="6">
+        <v>0.304265</v>
+      </c>
+      <c r="E134" s="6">
+        <v>0.313215</v>
+      </c>
+      <c r="F134" s="6">
+        <v>0.293659</v>
+      </c>
+      <c r="G134" s="6">
+        <v>0.266177</v>
+      </c>
+      <c r="H134" s="6">
+        <v>0.28564</v>
       </c>
       <c r="I134" s="4">
         <v>16</v>
       </c>
-      <c r="J134" s="7">
+      <c r="J134" s="6">
         <v>0.278275</v>
       </c>
-      <c r="K134" s="7">
+      <c r="K134" s="6">
         <v>0.263727</v>
       </c>
-      <c r="L134" s="9"/>
-      <c r="M134" s="9"/>
-      <c r="N134" s="9"/>
-      <c r="O134" s="9"/>
-      <c r="P134" s="9"/>
+      <c r="L134" s="6">
+        <v>0.265133</v>
+      </c>
+      <c r="M134" s="6">
+        <v>0.260986</v>
+      </c>
+      <c r="N134" s="6">
+        <v>0.259884</v>
+      </c>
+      <c r="O134" s="6">
+        <v>0.245174</v>
+      </c>
+      <c r="P134" s="6">
+        <v>0.254157</v>
+      </c>
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="6">
         <v>0.287527</v>
       </c>
-      <c r="C135" s="7">
+      <c r="C135" s="6">
         <v>0.312005</v>
       </c>
-      <c r="D135" s="7">
-        <v>0</v>
-      </c>
-      <c r="E135" s="7">
-        <v>0</v>
-      </c>
-      <c r="F135" s="7">
-        <v>0</v>
-      </c>
-      <c r="G135" s="7">
-        <v>0</v>
-      </c>
-      <c r="H135" s="7">
-        <v>0</v>
+      <c r="D135" s="6">
+        <v>0.293508</v>
+      </c>
+      <c r="E135" s="6">
+        <v>0.31394</v>
+      </c>
+      <c r="F135" s="6">
+        <v>0.2986</v>
+      </c>
+      <c r="G135" s="6">
+        <v>0.278252</v>
+      </c>
+      <c r="H135" s="6">
+        <v>0.294752</v>
       </c>
       <c r="I135" s="4">
         <v>16</v>
       </c>
-      <c r="J135" s="7">
+      <c r="J135" s="6">
         <v>0.265676</v>
       </c>
-      <c r="K135" s="7">
+      <c r="K135" s="6">
         <v>0.263543</v>
       </c>
-      <c r="L135" s="9"/>
-      <c r="M135" s="9"/>
-      <c r="N135" s="9"/>
-      <c r="O135" s="9"/>
-      <c r="P135" s="9"/>
+      <c r="L135" s="6">
+        <v>0.268471</v>
+      </c>
+      <c r="M135" s="6">
+        <v>0.263776</v>
+      </c>
+      <c r="N135" s="6">
+        <v>0.254981</v>
+      </c>
+      <c r="O135" s="6">
+        <v>0.26297</v>
+      </c>
+      <c r="P135" s="6">
+        <v>0.293957</v>
+      </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="6">
         <v>0.289587</v>
       </c>
-      <c r="C136" s="7">
+      <c r="C136" s="6">
         <v>0.326318</v>
       </c>
-      <c r="D136" s="7">
-        <v>0</v>
-      </c>
-      <c r="E136" s="7">
-        <v>0</v>
-      </c>
-      <c r="F136" s="7">
-        <v>0</v>
-      </c>
-      <c r="G136" s="7">
-        <v>0</v>
-      </c>
-      <c r="H136" s="7">
-        <v>0</v>
+      <c r="D136" s="6">
+        <v>0.304722</v>
+      </c>
+      <c r="E136" s="6">
+        <v>0.327364</v>
+      </c>
+      <c r="F136" s="6">
+        <v>0.310841</v>
+      </c>
+      <c r="G136" s="6">
+        <v>0.28899</v>
+      </c>
+      <c r="H136" s="6">
+        <v>0.289718</v>
       </c>
       <c r="I136" s="4">
         <v>16</v>
       </c>
-      <c r="J136" s="7">
+      <c r="J136" s="6">
         <v>0.268206</v>
       </c>
-      <c r="K136" s="7">
+      <c r="K136" s="6">
         <v>0.250079</v>
       </c>
-      <c r="L136" s="9"/>
-      <c r="M136" s="9"/>
-      <c r="N136" s="9"/>
-      <c r="O136" s="9"/>
-      <c r="P136" s="9"/>
+      <c r="L136" s="6">
+        <v>0.259585</v>
+      </c>
+      <c r="M136" s="6">
+        <v>0.266227</v>
+      </c>
+      <c r="N136" s="6">
+        <v>0.238065</v>
+      </c>
+      <c r="O136" s="6">
+        <v>0.24865</v>
+      </c>
+      <c r="P136" s="6">
+        <v>0.277811</v>
+      </c>
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B137" s="7">
+      <c r="B137" s="6">
         <v>0.302773</v>
       </c>
-      <c r="C137" s="7">
+      <c r="C137" s="6">
         <v>0.303786</v>
       </c>
-      <c r="D137" s="7">
-        <v>0</v>
-      </c>
-      <c r="E137" s="7">
-        <v>0</v>
-      </c>
-      <c r="F137" s="7">
-        <v>0</v>
-      </c>
-      <c r="G137" s="7">
-        <v>0</v>
-      </c>
-      <c r="H137" s="7">
-        <v>0</v>
+      <c r="D137" s="6">
+        <v>0.304694</v>
+      </c>
+      <c r="E137" s="6">
+        <v>0.322793</v>
+      </c>
+      <c r="F137" s="6">
+        <v>0.289096</v>
+      </c>
+      <c r="G137" s="6">
+        <v>0.281809</v>
+      </c>
+      <c r="H137" s="6">
+        <v>0.302015</v>
       </c>
       <c r="I137" s="4">
         <v>16</v>
       </c>
-      <c r="J137" s="7">
+      <c r="J137" s="6">
         <v>0.274784</v>
       </c>
-      <c r="K137" s="7">
+      <c r="K137" s="6">
         <v>0.273923</v>
       </c>
-      <c r="L137" s="9"/>
-      <c r="M137" s="9"/>
-      <c r="N137" s="9"/>
-      <c r="O137" s="9"/>
-      <c r="P137" s="9"/>
+      <c r="L137" s="6">
+        <v>0.270272</v>
+      </c>
+      <c r="M137" s="6">
+        <v>0.276757</v>
+      </c>
+      <c r="N137" s="6">
+        <v>0.273246</v>
+      </c>
+      <c r="O137" s="6">
+        <v>0.27757</v>
+      </c>
+      <c r="P137" s="6">
+        <v>0.291298</v>
+      </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="6">
         <v>0.263164</v>
       </c>
-      <c r="C138" s="7">
+      <c r="C138" s="6">
         <v>0.284056</v>
       </c>
-      <c r="D138" s="7">
+      <c r="D138" s="6">
         <v>0.287797</v>
       </c>
-      <c r="E138" s="7">
+      <c r="E138" s="6">
         <v>0.290794</v>
       </c>
-      <c r="F138" s="7">
+      <c r="F138" s="6">
         <v>0.286054</v>
       </c>
-      <c r="G138" s="7">
+      <c r="G138" s="6">
         <v>0.253974</v>
       </c>
-      <c r="H138" s="7">
+      <c r="H138" s="6">
         <v>0.276458</v>
       </c>
       <c r="I138" s="4">
         <v>32</v>
       </c>
-      <c r="J138" s="7">
+      <c r="J138" s="6">
         <v>0.28192</v>
       </c>
-      <c r="K138" s="7">
+      <c r="K138" s="6">
         <v>0.263922</v>
       </c>
-      <c r="L138" s="9"/>
-      <c r="M138" s="9"/>
-      <c r="N138" s="9"/>
-      <c r="O138" s="9"/>
-      <c r="P138" s="9"/>
+      <c r="L138" s="6">
+        <v>0.261891</v>
+      </c>
+      <c r="M138" s="6">
+        <v>0.261995</v>
+      </c>
+      <c r="N138" s="6">
+        <v>0.246888</v>
+      </c>
+      <c r="O138" s="6">
+        <v>0.240277</v>
+      </c>
+      <c r="P138" s="6">
+        <v>0.254575</v>
+      </c>
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="6">
         <v>0.260731</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="6">
         <v>0.285664</v>
       </c>
-      <c r="D139" s="7">
+      <c r="D139" s="6">
         <v>0.2951</v>
       </c>
-      <c r="E139" s="7">
+      <c r="E139" s="6">
         <v>0.283833</v>
       </c>
-      <c r="F139" s="7">
+      <c r="F139" s="6">
         <v>0.281365</v>
       </c>
-      <c r="G139" s="7">
+      <c r="G139" s="6">
         <v>0.259848</v>
       </c>
-      <c r="H139" s="7">
+      <c r="H139" s="6">
         <v>0.271173</v>
       </c>
       <c r="I139" s="4">
         <v>32</v>
       </c>
-      <c r="J139" s="7">
+      <c r="J139" s="6">
         <v>0.262685</v>
       </c>
-      <c r="K139" s="7">
+      <c r="K139" s="6">
         <v>0.269192</v>
       </c>
-      <c r="L139" s="9"/>
-      <c r="M139" s="9"/>
-      <c r="N139" s="9"/>
-      <c r="O139" s="9"/>
-      <c r="P139" s="9"/>
+      <c r="L139" s="6">
+        <v>0.2474</v>
+      </c>
+      <c r="M139" s="6">
+        <v>0.263231</v>
+      </c>
+      <c r="N139" s="6">
+        <v>0.233453</v>
+      </c>
+      <c r="O139" s="6">
+        <v>0.244294</v>
+      </c>
+      <c r="P139" s="6">
+        <v>0.278621</v>
+      </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="6">
         <v>0.261607</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="6">
         <v>0.274472</v>
       </c>
-      <c r="D140" s="7">
+      <c r="D140" s="6">
         <v>0.282863</v>
       </c>
-      <c r="E140" s="7">
+      <c r="E140" s="6">
         <v>0.288664</v>
       </c>
-      <c r="F140" s="7">
+      <c r="F140" s="6">
         <v>0.283986</v>
       </c>
-      <c r="G140" s="7">
+      <c r="G140" s="6">
         <v>0.259029</v>
       </c>
-      <c r="H140" s="7">
+      <c r="H140" s="6">
         <v>0.279226</v>
       </c>
       <c r="I140" s="4">
         <v>32</v>
       </c>
-      <c r="J140" s="7">
+      <c r="J140" s="6">
         <v>0.279118</v>
       </c>
-      <c r="K140" s="7">
+      <c r="K140" s="6">
         <v>0.258818</v>
       </c>
-      <c r="L140" s="9"/>
-      <c r="M140" s="9"/>
-      <c r="N140" s="9"/>
-      <c r="O140" s="9"/>
-      <c r="P140" s="9"/>
+      <c r="L140" s="6">
+        <v>0.271303</v>
+      </c>
+      <c r="M140" s="6">
+        <v>0.267003</v>
+      </c>
+      <c r="N140" s="6">
+        <v>0.266254</v>
+      </c>
+      <c r="O140" s="6">
+        <v>0.259708</v>
+      </c>
+      <c r="P140" s="6">
+        <v>0.274861</v>
+      </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B141" s="7">
+      <c r="B141" s="6">
         <v>0.270748</v>
       </c>
-      <c r="C141" s="7">
+      <c r="C141" s="6">
         <v>0.270532</v>
       </c>
-      <c r="D141" s="7">
+      <c r="D141" s="6">
         <v>0.293239</v>
       </c>
-      <c r="E141" s="7">
+      <c r="E141" s="6">
         <v>0.295566</v>
       </c>
-      <c r="F141" s="7">
+      <c r="F141" s="6">
         <v>0.293702</v>
       </c>
-      <c r="G141" s="7">
+      <c r="G141" s="6">
         <v>0.267414</v>
       </c>
-      <c r="H141" s="7">
+      <c r="H141" s="6">
         <v>0.27961</v>
       </c>
       <c r="I141" s="4">
         <v>32</v>
       </c>
-      <c r="J141" s="7">
+      <c r="J141" s="6">
         <v>0.275566</v>
       </c>
-      <c r="K141" s="7">
+      <c r="K141" s="6">
         <v>0.252969</v>
       </c>
-      <c r="L141" s="9"/>
-      <c r="M141" s="9"/>
-      <c r="N141" s="9"/>
-      <c r="O141" s="9"/>
-      <c r="P141" s="9"/>
+      <c r="L141" s="6">
+        <v>0.262296</v>
+      </c>
+      <c r="M141" s="6">
+        <v>0.258233</v>
+      </c>
+      <c r="N141" s="6">
+        <v>0.24587</v>
+      </c>
+      <c r="O141" s="6">
+        <v>0.249635</v>
+      </c>
+      <c r="P141" s="6">
+        <v>0.275681</v>
+      </c>
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="6">
         <v>0.276673</v>
       </c>
-      <c r="C142" s="7">
+      <c r="C142" s="6">
         <v>0.299689</v>
       </c>
-      <c r="D142" s="7">
-        <v>0</v>
-      </c>
-      <c r="E142" s="7">
-        <v>0</v>
-      </c>
-      <c r="F142" s="7">
-        <v>0</v>
-      </c>
-      <c r="G142" s="7">
-        <v>0</v>
-      </c>
-      <c r="H142" s="7">
-        <v>0</v>
+      <c r="D142" s="6">
+        <v>0.300976</v>
+      </c>
+      <c r="E142" s="6">
+        <v>0.305526</v>
+      </c>
+      <c r="F142" s="6">
+        <v>0.28558</v>
+      </c>
+      <c r="G142" s="6">
+        <v>0.269032</v>
+      </c>
+      <c r="H142" s="6">
+        <v>0.275656</v>
       </c>
       <c r="I142" s="4">
         <v>32</v>
       </c>
-      <c r="J142" s="7">
+      <c r="J142" s="6">
         <v>0.292304</v>
       </c>
-      <c r="K142" s="7">
+      <c r="K142" s="6">
         <v>0.266614</v>
       </c>
-      <c r="L142" s="9"/>
-      <c r="M142" s="9"/>
-      <c r="N142" s="9"/>
-      <c r="O142" s="9"/>
-      <c r="P142" s="9"/>
+      <c r="L142" s="6">
+        <v>0.264698</v>
+      </c>
+      <c r="M142" s="6">
+        <v>0.266427</v>
+      </c>
+      <c r="N142" s="6">
+        <v>0.268437</v>
+      </c>
+      <c r="O142" s="6">
+        <v>0.255045</v>
+      </c>
+      <c r="P142" s="6">
+        <v>0.266981</v>
+      </c>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B143" s="7">
+      <c r="B143" s="6">
         <v>0.251693</v>
       </c>
-      <c r="C143" s="7">
+      <c r="C143" s="6">
         <v>0.277986</v>
       </c>
-      <c r="D143" s="7">
+      <c r="D143" s="6">
         <v>0.303356</v>
       </c>
-      <c r="E143" s="7">
+      <c r="E143" s="6">
         <v>0.297265</v>
       </c>
-      <c r="F143" s="7">
+      <c r="F143" s="6">
         <v>0.29102</v>
       </c>
-      <c r="G143" s="7">
+      <c r="G143" s="6">
         <v>0.25121</v>
       </c>
-      <c r="H143" s="7">
+      <c r="H143" s="6">
         <v>0.260116</v>
       </c>
       <c r="I143" s="4">
         <v>64</v>
       </c>
-      <c r="J143" s="7">
+      <c r="J143" s="6">
         <v>0.280945</v>
       </c>
-      <c r="K143" s="7">
+      <c r="K143" s="6">
         <v>0.269494</v>
       </c>
-      <c r="L143" s="9"/>
-      <c r="M143" s="9"/>
-      <c r="N143" s="9"/>
-      <c r="O143" s="9"/>
-      <c r="P143" s="9"/>
+      <c r="L143" s="6">
+        <v>0.243886</v>
+      </c>
+      <c r="M143" s="6">
+        <v>0.259139</v>
+      </c>
+      <c r="N143" s="6">
+        <v>0.258217</v>
+      </c>
+      <c r="O143" s="6">
+        <v>0.257655</v>
+      </c>
+      <c r="P143" s="6">
+        <v>0.251063</v>
+      </c>
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="6">
         <v>0.25318</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="6">
         <v>0.277367</v>
       </c>
-      <c r="D144" s="7">
+      <c r="D144" s="6">
         <v>0.287973</v>
       </c>
-      <c r="E144" s="7">
+      <c r="E144" s="6">
         <v>0.279352</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F144" s="6">
         <v>0.282055</v>
       </c>
-      <c r="G144" s="7">
+      <c r="G144" s="6">
         <v>0.251475</v>
       </c>
-      <c r="H144" s="7">
+      <c r="H144" s="6">
         <v>0.269438</v>
       </c>
       <c r="I144" s="4">
         <v>64</v>
       </c>
-      <c r="J144" s="7">
+      <c r="J144" s="6">
         <v>0.270196</v>
       </c>
-      <c r="K144" s="7">
+      <c r="K144" s="6">
         <v>0.257122</v>
       </c>
-      <c r="L144" s="9"/>
-      <c r="M144" s="9"/>
-      <c r="N144" s="9"/>
-      <c r="O144" s="9"/>
-      <c r="P144" s="9"/>
+      <c r="L144" s="6">
+        <v>0.263287</v>
+      </c>
+      <c r="M144" s="6">
+        <v>0.262631</v>
+      </c>
+      <c r="N144" s="6">
+        <v>0.244072</v>
+      </c>
+      <c r="O144" s="6">
+        <v>0.254213</v>
+      </c>
+      <c r="P144" s="6">
+        <v>0.26669</v>
+      </c>
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="6">
         <v>0.252066</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C145" s="6">
         <v>0.27117</v>
       </c>
-      <c r="D145" s="7">
+      <c r="D145" s="6">
         <v>0.287698</v>
       </c>
-      <c r="E145" s="7">
+      <c r="E145" s="6">
         <v>0.291448</v>
       </c>
-      <c r="F145" s="7">
+      <c r="F145" s="6">
         <v>0.285061</v>
       </c>
-      <c r="G145" s="7">
+      <c r="G145" s="6">
         <v>0.250357</v>
       </c>
-      <c r="H145" s="7">
+      <c r="H145" s="6">
         <v>0.265004</v>
       </c>
       <c r="I145" s="4">
         <v>64</v>
       </c>
-      <c r="J145" s="7">
+      <c r="J145" s="6">
         <v>0.265061</v>
       </c>
-      <c r="K145" s="7">
+      <c r="K145" s="6">
         <v>0.26878</v>
       </c>
-      <c r="L145" s="9"/>
-      <c r="M145" s="9"/>
-      <c r="N145" s="9"/>
-      <c r="O145" s="9"/>
-      <c r="P145" s="9"/>
+      <c r="L145" s="6">
+        <v>0.222313</v>
+      </c>
+      <c r="M145" s="6">
+        <v>0.248907</v>
+      </c>
+      <c r="N145" s="6">
+        <v>0.237713</v>
+      </c>
+      <c r="O145" s="6">
+        <v>0.252879</v>
+      </c>
+      <c r="P145" s="6">
+        <v>0.259431</v>
+      </c>
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="6">
         <v>0.253602</v>
       </c>
-      <c r="C146" s="7">
+      <c r="C146" s="6">
         <v>0.279723</v>
       </c>
-      <c r="D146" s="7">
-        <v>0</v>
-      </c>
-      <c r="E146" s="7">
-        <v>0</v>
-      </c>
-      <c r="F146" s="7">
-        <v>0</v>
-      </c>
-      <c r="G146" s="7">
+      <c r="D146" s="6">
+        <v>0.293647</v>
+      </c>
+      <c r="E146" s="6">
+        <v>0.301168</v>
+      </c>
+      <c r="F146" s="6">
+        <v>0.288026</v>
+      </c>
+      <c r="G146" s="6">
         <v>0.251114</v>
       </c>
-      <c r="H146" s="7">
+      <c r="H146" s="6">
         <v>0.269113</v>
       </c>
       <c r="I146" s="4">
         <v>64</v>
       </c>
-      <c r="J146" s="7">
+      <c r="J146" s="6">
         <v>0.250292</v>
       </c>
-      <c r="K146" s="7">
+      <c r="K146" s="6">
         <v>0.259517</v>
       </c>
-      <c r="L146" s="9"/>
-      <c r="M146" s="9"/>
-      <c r="N146" s="9"/>
-      <c r="O146" s="9"/>
-      <c r="P146" s="9"/>
+      <c r="L146" s="6">
+        <v>0.243084</v>
+      </c>
+      <c r="M146" s="6">
+        <v>0.255264</v>
+      </c>
+      <c r="N146" s="6">
+        <v>0.240328</v>
+      </c>
+      <c r="O146" s="6">
+        <v>0.250582</v>
+      </c>
+      <c r="P146" s="6">
+        <v>0.2614</v>
+      </c>
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="6">
         <v>0.261364</v>
       </c>
-      <c r="C147" s="7">
+      <c r="C147" s="6">
         <v>0.265174</v>
       </c>
-      <c r="D147" s="7">
+      <c r="D147" s="6">
         <v>0.364465</v>
       </c>
-      <c r="E147" s="7">
+      <c r="E147" s="6">
         <v>0.367993</v>
       </c>
-      <c r="F147" s="7">
-        <v>0</v>
-      </c>
-      <c r="G147" s="7">
-        <v>0</v>
-      </c>
-      <c r="H147" s="7">
-        <v>0</v>
+      <c r="F147" s="6">
+        <v>0.290744</v>
+      </c>
+      <c r="G147" s="6">
+        <v>0.254528</v>
+      </c>
+      <c r="H147" s="6">
+        <v>0.276261</v>
       </c>
       <c r="I147" s="4">
         <v>64</v>
       </c>
-      <c r="J147" s="7">
+      <c r="J147" s="6">
         <v>0.271128</v>
       </c>
-      <c r="K147" s="7">
+      <c r="K147" s="6">
         <v>0.264287</v>
       </c>
-      <c r="L147" s="9"/>
-      <c r="M147" s="9"/>
-      <c r="N147" s="9"/>
-      <c r="O147" s="9"/>
-      <c r="P147" s="9"/>
+      <c r="L147" s="6">
+        <v>0.243644</v>
+      </c>
+      <c r="M147" s="6">
+        <v>0.250132</v>
+      </c>
+      <c r="N147" s="6">
+        <v>0.260518</v>
+      </c>
+      <c r="O147" s="6">
+        <v>0.261666</v>
+      </c>
+      <c r="P147" s="6">
+        <v>0.280881</v>
+      </c>
     </row>
     <row r="148" spans="1:16">
-      <c r="A148" s="8"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="8"/>
-      <c r="J148" s="7"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="9"/>
-      <c r="M148" s="9"/>
-      <c r="N148" s="9"/>
-      <c r="O148" s="9"/>
-      <c r="P148" s="9"/>
+      <c r="A148" s="7"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="6"/>
+      <c r="K148" s="6"/>
+      <c r="L148" s="8"/>
+      <c r="M148" s="8"/>
+      <c r="N148" s="8"/>
+      <c r="O148" s="8"/>
+      <c r="P148" s="8"/>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B149" s="7">
+      <c r="B149" s="6">
         <v>0.126944</v>
       </c>
-      <c r="C149" s="7">
+      <c r="C149" s="6">
         <v>0.20655</v>
       </c>
-      <c r="D149" s="7">
+      <c r="D149" s="6">
         <v>0.192765</v>
       </c>
-      <c r="E149" s="7">
+      <c r="E149" s="6">
         <v>0.135866</v>
       </c>
-      <c r="F149" s="7">
+      <c r="F149" s="6">
         <v>0.154117</v>
       </c>
       <c r="G149" s="6">
         <v>0.09406</v>
       </c>
-      <c r="H149" s="7">
+      <c r="H149" s="6">
         <v>0.134953</v>
       </c>
       <c r="I149" s="4">
         <v>8</v>
       </c>
-      <c r="J149" s="7">
+      <c r="J149" s="6">
         <v>0.0422952</v>
       </c>
-      <c r="K149" s="7">
+      <c r="K149" s="6">
         <v>0.0376449</v>
       </c>
-      <c r="L149" s="7">
+      <c r="L149" s="6">
         <v>0.042678</v>
       </c>
-      <c r="M149" s="7">
+      <c r="M149" s="6">
         <v>0.044299</v>
       </c>
       <c r="N149" s="6">
@@ -8450,40 +8646,40 @@
       <c r="B150" s="6">
         <v>0.10786</v>
       </c>
-      <c r="C150" s="7">
+      <c r="C150" s="6">
         <v>0.176656</v>
       </c>
-      <c r="D150" s="7">
+      <c r="D150" s="6">
         <v>0.185637</v>
       </c>
-      <c r="E150" s="7">
+      <c r="E150" s="6">
         <v>0.184495</v>
       </c>
-      <c r="F150" s="7">
+      <c r="F150" s="6">
         <v>0.163392</v>
       </c>
-      <c r="G150" s="7">
+      <c r="G150" s="6">
         <v>0.146021</v>
       </c>
-      <c r="H150" s="7">
+      <c r="H150" s="6">
         <v>0.157534</v>
       </c>
       <c r="I150" s="4">
         <v>8</v>
       </c>
-      <c r="J150" s="7">
+      <c r="J150" s="6">
         <v>0.04243</v>
       </c>
-      <c r="K150" s="7">
+      <c r="K150" s="6">
         <v>0.037931</v>
       </c>
-      <c r="L150" s="7">
+      <c r="L150" s="6">
         <v>0.045392</v>
       </c>
-      <c r="M150" s="7">
+      <c r="M150" s="6">
         <v>0.044224</v>
       </c>
-      <c r="N150" s="7">
+      <c r="N150" s="6">
         <v>0.03965</v>
       </c>
       <c r="O150" s="6">
@@ -8497,22 +8693,22 @@
       <c r="A151" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B151" s="7">
+      <c r="B151" s="6">
         <v>0.151002</v>
       </c>
-      <c r="C151" s="7">
+      <c r="C151" s="6">
         <v>0.202372</v>
       </c>
       <c r="D151" s="6">
         <v>0.125268</v>
       </c>
-      <c r="E151" s="7">
+      <c r="E151" s="6">
         <v>0.229226</v>
       </c>
       <c r="F151" s="6">
         <v>0.097051</v>
       </c>
-      <c r="G151" s="7">
+      <c r="G151" s="6">
         <v>0.212826</v>
       </c>
       <c r="H151" s="6">
@@ -8521,45 +8717,45 @@
       <c r="I151" s="4">
         <v>8</v>
       </c>
-      <c r="J151" s="7">
+      <c r="J151" s="6">
         <v>0.0424212</v>
       </c>
-      <c r="K151" s="7">
+      <c r="K151" s="6">
         <v>0.0432424</v>
       </c>
-      <c r="L151" s="7">
+      <c r="L151" s="6">
         <v>0.037516</v>
       </c>
-      <c r="M151" s="7">
+      <c r="M151" s="6">
         <v>0.038569</v>
       </c>
-      <c r="N151" s="7">
+      <c r="N151" s="6">
         <v>0.035822</v>
       </c>
-      <c r="O151" s="7">
+      <c r="O151" s="6">
         <v>0.03805</v>
       </c>
-      <c r="P151" s="7">
-        <v>0</v>
+      <c r="P151" s="6">
+        <v>0.036829</v>
       </c>
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="6">
         <v>0.147176</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="6">
         <v>0.202141</v>
       </c>
-      <c r="D152" s="7">
+      <c r="D152" s="6">
         <v>0.218998</v>
       </c>
-      <c r="E152" s="7">
+      <c r="E152" s="6">
         <v>0.188635</v>
       </c>
-      <c r="F152" s="7">
+      <c r="F152" s="6">
         <v>0.19944</v>
       </c>
       <c r="G152" s="6">
@@ -8571,36 +8767,36 @@
       <c r="I152" s="4">
         <v>8</v>
       </c>
-      <c r="J152" s="7">
+      <c r="J152" s="6">
         <v>0.0417402</v>
       </c>
-      <c r="K152" s="7">
+      <c r="K152" s="6">
         <v>0.0442679</v>
       </c>
-      <c r="L152" s="7">
-        <v>0</v>
-      </c>
-      <c r="M152" s="7">
-        <v>0</v>
-      </c>
-      <c r="N152" s="7">
-        <v>0</v>
-      </c>
-      <c r="O152" s="7">
-        <v>0</v>
-      </c>
-      <c r="P152" s="7">
-        <v>0</v>
+      <c r="L152" s="6">
+        <v>0.044643</v>
+      </c>
+      <c r="M152" s="6">
+        <v>0.040011</v>
+      </c>
+      <c r="N152" s="6">
+        <v>0.03576</v>
+      </c>
+      <c r="O152" s="6">
+        <v>0.035892</v>
+      </c>
+      <c r="P152" s="6">
+        <v>0.036337</v>
       </c>
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B153" s="7">
+      <c r="B153" s="6">
         <v>0.137893</v>
       </c>
-      <c r="C153" s="7">
+      <c r="C153" s="6">
         <v>0.141569</v>
       </c>
       <c r="D153" s="6">
@@ -8612,7 +8808,7 @@
       <c r="F153" s="6">
         <v>0.12258</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="6">
         <v>0.163349</v>
       </c>
       <c r="H153" s="6">
@@ -8621,26 +8817,26 @@
       <c r="I153" s="4">
         <v>8</v>
       </c>
-      <c r="J153" s="7">
+      <c r="J153" s="6">
         <v>0.0433845</v>
       </c>
-      <c r="K153" s="7">
+      <c r="K153" s="6">
         <v>0.0356731</v>
       </c>
-      <c r="L153" s="7">
-        <v>0</v>
-      </c>
-      <c r="M153" s="7">
-        <v>0</v>
-      </c>
-      <c r="N153" s="7">
-        <v>0</v>
-      </c>
-      <c r="O153" s="7">
-        <v>0</v>
-      </c>
-      <c r="P153" s="7">
-        <v>0</v>
+      <c r="L153" s="6">
+        <v>0.044957</v>
+      </c>
+      <c r="M153" s="6">
+        <v>0.043433</v>
+      </c>
+      <c r="N153" s="6">
+        <v>0.038906</v>
+      </c>
+      <c r="O153" s="6">
+        <v>0.032446</v>
+      </c>
+      <c r="P153" s="6">
+        <v>0.034273</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8650,34 +8846,34 @@
       <c r="B154" s="6">
         <v>0.101808</v>
       </c>
-      <c r="C154" s="7">
+      <c r="C154" s="6">
         <v>0.108806</v>
       </c>
-      <c r="D154" s="7">
+      <c r="D154" s="6">
         <v>0.153961</v>
       </c>
-      <c r="E154" s="7">
+      <c r="E154" s="6">
         <v>0.153369</v>
       </c>
-      <c r="F154" s="7">
+      <c r="F154" s="6">
         <v>0.169612</v>
       </c>
-      <c r="G154" s="7">
+      <c r="G154" s="6">
         <v>0.112874</v>
       </c>
-      <c r="H154" s="7">
+      <c r="H154" s="6">
         <v>0.114634</v>
       </c>
       <c r="I154" s="4">
         <v>16</v>
       </c>
-      <c r="J154" s="7">
+      <c r="J154" s="6">
         <v>0.0391454</v>
       </c>
-      <c r="K154" s="7">
+      <c r="K154" s="6">
         <v>0.0372153</v>
       </c>
-      <c r="L154" s="7">
+      <c r="L154" s="6">
         <v>0.03804</v>
       </c>
       <c r="M154" s="6">
@@ -8697,16 +8893,16 @@
       <c r="A155" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B155" s="7">
+      <c r="B155" s="6">
         <v>0.130315</v>
       </c>
-      <c r="C155" s="7">
+      <c r="C155" s="6">
         <v>0.154415</v>
       </c>
-      <c r="D155" s="7">
+      <c r="D155" s="6">
         <v>0.141914</v>
       </c>
-      <c r="E155" s="7">
+      <c r="E155" s="6">
         <v>0.144</v>
       </c>
       <c r="F155" s="6">
@@ -8724,22 +8920,22 @@
       <c r="J155" s="6">
         <v>0.0321329</v>
       </c>
-      <c r="K155" s="7">
+      <c r="K155" s="6">
         <v>0.0395881</v>
       </c>
-      <c r="L155" s="7">
+      <c r="L155" s="6">
         <v>0.038232</v>
       </c>
-      <c r="M155" s="7">
+      <c r="M155" s="6">
         <v>0.035189</v>
       </c>
-      <c r="N155" s="7">
+      <c r="N155" s="6">
         <v>0.034156</v>
       </c>
-      <c r="O155" s="7">
+      <c r="O155" s="6">
         <v>0.035797</v>
       </c>
-      <c r="P155" s="7">
+      <c r="P155" s="6">
         <v>0.037019</v>
       </c>
     </row>
@@ -8747,19 +8943,19 @@
       <c r="A156" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B156" s="7">
+      <c r="B156" s="6">
         <v>0.117551</v>
       </c>
-      <c r="C156" s="7">
+      <c r="C156" s="6">
         <v>0.155259</v>
       </c>
-      <c r="D156" s="7">
+      <c r="D156" s="6">
         <v>0.132194</v>
       </c>
       <c r="E156" s="6">
         <v>0.115381</v>
       </c>
-      <c r="F156" s="7">
+      <c r="F156" s="6">
         <v>0.120164</v>
       </c>
       <c r="G156" s="6">
@@ -8771,48 +8967,48 @@
       <c r="I156" s="4">
         <v>16</v>
       </c>
-      <c r="J156" s="7">
+      <c r="J156" s="6">
         <v>0.0362122</v>
       </c>
-      <c r="K156" s="7">
+      <c r="K156" s="6">
         <v>0.0374768</v>
       </c>
-      <c r="L156" s="7">
-        <v>0</v>
-      </c>
-      <c r="M156" s="7">
-        <v>0</v>
-      </c>
-      <c r="N156" s="7">
-        <v>0</v>
-      </c>
-      <c r="O156" s="7">
-        <v>0</v>
-      </c>
-      <c r="P156" s="7">
-        <v>0</v>
+      <c r="L156" s="6">
+        <v>0.036863</v>
+      </c>
+      <c r="M156" s="6">
+        <v>0.036203</v>
+      </c>
+      <c r="N156" s="6">
+        <v>0.034014</v>
+      </c>
+      <c r="O156" s="6">
+        <v>0.0349</v>
+      </c>
+      <c r="P156" s="6">
+        <v>0.036183</v>
       </c>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B157" s="7">
+      <c r="B157" s="6">
         <v>0.115722</v>
       </c>
-      <c r="C157" s="7">
+      <c r="C157" s="6">
         <v>0.187678</v>
       </c>
-      <c r="D157" s="7">
+      <c r="D157" s="6">
         <v>0.16396</v>
       </c>
-      <c r="E157" s="7">
+      <c r="E157" s="6">
         <v>0.158701</v>
       </c>
       <c r="F157" s="6">
         <v>0.107422</v>
       </c>
-      <c r="G157" s="7">
+      <c r="G157" s="6">
         <v>0.122569</v>
       </c>
       <c r="H157" s="6">
@@ -8821,48 +9017,48 @@
       <c r="I157" s="4">
         <v>16</v>
       </c>
-      <c r="J157" s="7">
+      <c r="J157" s="6">
         <v>0.035583</v>
       </c>
-      <c r="K157" s="7">
+      <c r="K157" s="6">
         <v>0.0405208</v>
       </c>
-      <c r="L157" s="7">
-        <v>0</v>
-      </c>
-      <c r="M157" s="7">
-        <v>0</v>
-      </c>
-      <c r="N157" s="7">
-        <v>0</v>
-      </c>
-      <c r="O157" s="7">
-        <v>0</v>
-      </c>
-      <c r="P157" s="7">
-        <v>0</v>
+      <c r="L157" s="6">
+        <v>0.037242</v>
+      </c>
+      <c r="M157" s="6">
+        <v>0.037309</v>
+      </c>
+      <c r="N157" s="6">
+        <v>0.03329</v>
+      </c>
+      <c r="O157" s="6">
+        <v>0.033747</v>
+      </c>
+      <c r="P157" s="6">
+        <v>0.039867</v>
       </c>
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="6">
         <v>0.103697</v>
       </c>
-      <c r="C158" s="7">
+      <c r="C158" s="6">
         <v>0.108473</v>
       </c>
-      <c r="D158" s="7">
+      <c r="D158" s="6">
         <v>0.166776</v>
       </c>
-      <c r="E158" s="7">
+      <c r="E158" s="6">
         <v>0.228218</v>
       </c>
-      <c r="F158" s="7">
+      <c r="F158" s="6">
         <v>0.136272</v>
       </c>
-      <c r="G158" s="7">
+      <c r="G158" s="6">
         <v>0.122839</v>
       </c>
       <c r="H158" s="6">
@@ -8871,67 +9067,67 @@
       <c r="I158" s="4">
         <v>16</v>
       </c>
-      <c r="J158" s="7">
+      <c r="J158" s="6">
         <v>0.0357567</v>
       </c>
-      <c r="K158" s="7">
+      <c r="K158" s="6">
         <v>0.0339016</v>
       </c>
-      <c r="L158" s="7">
-        <v>0</v>
-      </c>
-      <c r="M158" s="7">
-        <v>0</v>
-      </c>
-      <c r="N158" s="7">
-        <v>0</v>
-      </c>
-      <c r="O158" s="7">
-        <v>0</v>
-      </c>
-      <c r="P158" s="7">
-        <v>0</v>
+      <c r="L158" s="6">
+        <v>0.036747</v>
+      </c>
+      <c r="M158" s="6">
+        <v>0.038166</v>
+      </c>
+      <c r="N158" s="6">
+        <v>0.03416</v>
+      </c>
+      <c r="O158" s="6">
+        <v>0.036082</v>
+      </c>
+      <c r="P158" s="6">
+        <v>0.041252</v>
       </c>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B159" s="7">
+      <c r="B159" s="6">
         <v>0.107611</v>
       </c>
-      <c r="C159" s="7">
+      <c r="C159" s="6">
         <v>0.108467</v>
       </c>
-      <c r="D159" s="7">
+      <c r="D159" s="6">
         <v>0.163285</v>
       </c>
-      <c r="E159" s="7">
+      <c r="E159" s="6">
         <v>0.163885</v>
       </c>
-      <c r="F159" s="7">
+      <c r="F159" s="6">
         <v>0.133471</v>
       </c>
       <c r="G159" s="6">
         <v>0.096517</v>
       </c>
-      <c r="H159" s="7">
+      <c r="H159" s="6">
         <v>0.141286</v>
       </c>
       <c r="I159" s="4">
         <v>32</v>
       </c>
-      <c r="J159" s="7">
+      <c r="J159" s="6">
         <v>0.0362152</v>
       </c>
-      <c r="K159" s="7">
+      <c r="K159" s="6">
         <v>0.0326036</v>
       </c>
-      <c r="L159" s="7">
+      <c r="L159" s="6">
         <v>0.035622</v>
       </c>
-      <c r="M159" s="7">
-        <v>0</v>
+      <c r="M159" s="6">
+        <v>0.035467</v>
       </c>
       <c r="N159" s="6">
         <v>0.032187</v>
@@ -8939,7 +9135,7 @@
       <c r="O159" s="6">
         <v>0.032115</v>
       </c>
-      <c r="P159" s="7">
+      <c r="P159" s="6">
         <v>0.034142</v>
       </c>
     </row>
@@ -8947,10 +9143,10 @@
       <c r="A160" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B160" s="7">
+      <c r="B160" s="6">
         <v>0.103825</v>
       </c>
-      <c r="C160" s="7">
+      <c r="C160" s="6">
         <v>0.164423</v>
       </c>
       <c r="D160" s="6">
@@ -8959,10 +9155,10 @@
       <c r="E160" s="6">
         <v>0.101998</v>
       </c>
-      <c r="F160" s="7">
+      <c r="F160" s="6">
         <v>0.118113</v>
       </c>
-      <c r="G160" s="7">
+      <c r="G160" s="6">
         <v>0.110303</v>
       </c>
       <c r="H160" s="6">
@@ -8971,22 +9167,22 @@
       <c r="I160" s="4">
         <v>32</v>
       </c>
-      <c r="J160" s="7">
+      <c r="J160" s="6">
         <v>0.0379595</v>
       </c>
-      <c r="K160" s="7">
+      <c r="K160" s="6">
         <v>0.0316513</v>
       </c>
-      <c r="L160" s="7">
+      <c r="L160" s="6">
         <v>0.035448</v>
       </c>
-      <c r="M160" s="7">
+      <c r="M160" s="6">
         <v>0.037816</v>
       </c>
-      <c r="N160" s="7">
+      <c r="N160" s="6">
         <v>0.036565</v>
       </c>
-      <c r="O160" s="7">
+      <c r="O160" s="6">
         <v>0.032255</v>
       </c>
       <c r="P160" s="6">
@@ -8997,22 +9193,22 @@
       <c r="A161" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="6">
         <v>0.0901093</v>
       </c>
-      <c r="C161" s="7">
+      <c r="C161" s="6">
         <v>0.112444</v>
       </c>
-      <c r="D161" s="7">
+      <c r="D161" s="6">
         <v>0.148948</v>
       </c>
-      <c r="E161" s="7">
+      <c r="E161" s="6">
         <v>0.16041</v>
       </c>
-      <c r="F161" s="7">
+      <c r="F161" s="6">
         <v>0.135121</v>
       </c>
-      <c r="G161" s="7">
+      <c r="G161" s="6">
         <v>0.115694</v>
       </c>
       <c r="H161" s="6">
@@ -9021,42 +9217,42 @@
       <c r="I161" s="4">
         <v>32</v>
       </c>
-      <c r="J161" s="7">
+      <c r="J161" s="6">
         <v>0.0331405</v>
       </c>
-      <c r="K161" s="7">
+      <c r="K161" s="6">
         <v>0.0384587</v>
       </c>
-      <c r="L161" s="7">
-        <v>0</v>
-      </c>
-      <c r="M161" s="7">
-        <v>0</v>
-      </c>
-      <c r="N161" s="7">
-        <v>0</v>
-      </c>
-      <c r="O161" s="7">
-        <v>0</v>
-      </c>
-      <c r="P161" s="7">
-        <v>0</v>
+      <c r="L161" s="6">
+        <v>0.032937</v>
+      </c>
+      <c r="M161" s="6">
+        <v>0.033365</v>
+      </c>
+      <c r="N161" s="6">
+        <v>0.036912</v>
+      </c>
+      <c r="O161" s="6">
+        <v>0.035791</v>
+      </c>
+      <c r="P161" s="6">
+        <v>0.033437</v>
       </c>
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B162" s="7">
+      <c r="B162" s="6">
         <v>0.121179</v>
       </c>
-      <c r="C162" s="7">
+      <c r="C162" s="6">
         <v>0.134238</v>
       </c>
-      <c r="D162" s="7">
+      <c r="D162" s="6">
         <v>0.131682</v>
       </c>
-      <c r="E162" s="7">
+      <c r="E162" s="6">
         <v>0.1305</v>
       </c>
       <c r="F162" s="6">
@@ -9071,48 +9267,48 @@
       <c r="I162" s="4">
         <v>32</v>
       </c>
-      <c r="J162" s="7">
+      <c r="J162" s="6">
         <v>0.0330712</v>
       </c>
-      <c r="K162" s="7">
+      <c r="K162" s="6">
         <v>0.0338868</v>
       </c>
-      <c r="L162" s="7">
-        <v>0</v>
-      </c>
-      <c r="M162" s="7">
-        <v>0</v>
-      </c>
-      <c r="N162" s="7">
-        <v>0</v>
-      </c>
-      <c r="O162" s="7">
-        <v>0</v>
-      </c>
-      <c r="P162" s="7">
-        <v>0</v>
+      <c r="L162" s="6">
+        <v>0.033241</v>
+      </c>
+      <c r="M162" s="6">
+        <v>0.033715</v>
+      </c>
+      <c r="N162" s="6">
+        <v>0.031168</v>
+      </c>
+      <c r="O162" s="6">
+        <v>0.032405</v>
+      </c>
+      <c r="P162" s="6">
+        <v>0.038567</v>
       </c>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B163" s="7">
+      <c r="B163" s="6">
         <v>0.0904846</v>
       </c>
-      <c r="C163" s="7">
+      <c r="C163" s="6">
         <v>0.147704</v>
       </c>
-      <c r="D163" s="7">
+      <c r="D163" s="6">
         <v>0.121764</v>
       </c>
-      <c r="E163" s="7">
+      <c r="E163" s="6">
         <v>0.121571</v>
       </c>
-      <c r="F163" s="7">
+      <c r="F163" s="6">
         <v>0.111416</v>
       </c>
-      <c r="G163" s="7">
+      <c r="G163" s="6">
         <v>0.108488</v>
       </c>
       <c r="H163" s="6">
@@ -9121,48 +9317,48 @@
       <c r="I163" s="4">
         <v>32</v>
       </c>
-      <c r="J163" s="7">
+      <c r="J163" s="6">
         <v>0.0387067</v>
       </c>
-      <c r="K163" s="7">
+      <c r="K163" s="6">
         <v>0.036896</v>
       </c>
-      <c r="L163" s="7">
-        <v>0</v>
-      </c>
-      <c r="M163" s="7">
-        <v>0</v>
-      </c>
-      <c r="N163" s="7">
-        <v>0</v>
-      </c>
-      <c r="O163" s="7">
-        <v>0</v>
-      </c>
-      <c r="P163" s="7">
-        <v>0</v>
+      <c r="L163" s="6">
+        <v>0.032345</v>
+      </c>
+      <c r="M163" s="6">
+        <v>0.034224</v>
+      </c>
+      <c r="N163" s="6">
+        <v>0.03732</v>
+      </c>
+      <c r="O163" s="6">
+        <v>0.034324</v>
+      </c>
+      <c r="P163" s="6">
+        <v>0.036764</v>
       </c>
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B164" s="7">
+      <c r="B164" s="6">
         <v>0.115596</v>
       </c>
-      <c r="C164" s="7">
+      <c r="C164" s="6">
         <v>0.0991081</v>
       </c>
-      <c r="D164" s="7">
+      <c r="D164" s="6">
         <v>0.142646</v>
       </c>
-      <c r="E164" s="7">
+      <c r="E164" s="6">
         <v>0.141169</v>
       </c>
-      <c r="F164" s="7">
+      <c r="F164" s="6">
         <v>0.13092</v>
       </c>
-      <c r="G164" s="7">
+      <c r="G164" s="6">
         <v>0.106011</v>
       </c>
       <c r="H164" s="6">
@@ -9171,25 +9367,25 @@
       <c r="I164" s="4">
         <v>64</v>
       </c>
-      <c r="J164" s="7">
+      <c r="J164" s="6">
         <v>0.0319565</v>
       </c>
-      <c r="K164" s="7">
+      <c r="K164" s="6">
         <v>0.0335849</v>
       </c>
-      <c r="L164" s="7">
+      <c r="L164" s="6">
         <v>0.037502</v>
       </c>
-      <c r="M164" s="7">
+      <c r="M164" s="6">
         <v>0.034875</v>
       </c>
-      <c r="N164" s="7">
+      <c r="N164" s="6">
         <v>0.036377</v>
       </c>
       <c r="O164" s="6">
         <v>0.029883</v>
       </c>
-      <c r="P164" s="7">
+      <c r="P164" s="6">
         <v>0.037098</v>
       </c>
     </row>
@@ -9197,34 +9393,34 @@
       <c r="A165" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B165" s="7">
+      <c r="B165" s="6">
         <v>0.123882</v>
       </c>
       <c r="C165" s="6">
         <v>0.0939172</v>
       </c>
-      <c r="D165" s="7">
+      <c r="D165" s="6">
         <v>0.123117</v>
       </c>
-      <c r="E165" s="7">
+      <c r="E165" s="6">
         <v>0.122881</v>
       </c>
-      <c r="F165" s="7">
+      <c r="F165" s="6">
         <v>0.126771</v>
       </c>
-      <c r="G165" s="7">
+      <c r="G165" s="6">
         <v>0.099141</v>
       </c>
-      <c r="H165" s="7">
+      <c r="H165" s="6">
         <v>0.103991</v>
       </c>
       <c r="I165" s="4">
         <v>64</v>
       </c>
-      <c r="J165" s="7">
+      <c r="J165" s="6">
         <v>0.0372528</v>
       </c>
-      <c r="K165" s="7">
+      <c r="K165" s="6">
         <v>0.0372017</v>
       </c>
       <c r="L165" s="6">
@@ -9247,119 +9443,119 @@
       <c r="A166" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B166" s="7">
+      <c r="B166" s="6">
         <v>0.0980649</v>
       </c>
-      <c r="C166" s="7">
+      <c r="C166" s="6">
         <v>0.113789</v>
       </c>
-      <c r="D166" s="7">
+      <c r="D166" s="6">
         <v>0.143873</v>
       </c>
-      <c r="E166" s="7">
+      <c r="E166" s="6">
         <v>0.143647</v>
       </c>
-      <c r="F166" s="7">
+      <c r="F166" s="6">
         <v>0.115394</v>
       </c>
       <c r="G166" s="6">
         <v>0.092397</v>
       </c>
-      <c r="H166" s="7">
+      <c r="H166" s="6">
         <v>0.105341</v>
       </c>
       <c r="I166" s="4">
         <v>64</v>
       </c>
-      <c r="J166" s="7">
+      <c r="J166" s="6">
         <v>0.0383766</v>
       </c>
-      <c r="K166" s="7">
+      <c r="K166" s="6">
         <v>0.0374488</v>
       </c>
-      <c r="L166" s="7">
-        <v>0</v>
-      </c>
-      <c r="M166" s="7">
-        <v>0</v>
-      </c>
-      <c r="N166" s="7">
-        <v>0</v>
-      </c>
-      <c r="O166" s="7">
-        <v>0</v>
-      </c>
-      <c r="P166" s="7">
-        <v>0</v>
+      <c r="L166" s="6">
+        <v>0.033358</v>
+      </c>
+      <c r="M166" s="6">
+        <v>0.03333</v>
+      </c>
+      <c r="N166" s="6">
+        <v>0.031337</v>
+      </c>
+      <c r="O166" s="6">
+        <v>0.034752</v>
+      </c>
+      <c r="P166" s="6">
+        <v>0.031678</v>
       </c>
     </row>
     <row r="167" spans="1:16">
       <c r="A167" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B167" s="7">
+      <c r="B167" s="6">
         <v>0.102196</v>
       </c>
-      <c r="C167" s="7">
+      <c r="C167" s="6">
         <v>0.121754</v>
       </c>
-      <c r="D167" s="7">
+      <c r="D167" s="6">
         <v>0.165882</v>
       </c>
-      <c r="E167" s="7">
+      <c r="E167" s="6">
         <v>0.166028</v>
       </c>
-      <c r="F167" s="7">
+      <c r="F167" s="6">
         <v>0.116743</v>
       </c>
       <c r="G167" s="6">
         <v>0.10013</v>
       </c>
-      <c r="H167" s="7">
+      <c r="H167" s="6">
         <v>0.111919</v>
       </c>
       <c r="I167" s="4">
         <v>64</v>
       </c>
-      <c r="J167" s="7">
+      <c r="J167" s="6">
         <v>0.0360947</v>
       </c>
-      <c r="K167" s="7">
+      <c r="K167" s="6">
         <v>0.0357229</v>
       </c>
-      <c r="L167" s="7">
-        <v>0</v>
-      </c>
-      <c r="M167" s="7">
-        <v>0</v>
-      </c>
-      <c r="N167" s="7">
-        <v>0</v>
-      </c>
-      <c r="O167" s="7">
-        <v>0</v>
-      </c>
-      <c r="P167" s="7">
-        <v>0</v>
+      <c r="L167" s="6">
+        <v>0.032075</v>
+      </c>
+      <c r="M167" s="6">
+        <v>0.036008</v>
+      </c>
+      <c r="N167" s="6">
+        <v>0.038302</v>
+      </c>
+      <c r="O167" s="6">
+        <v>0.031702</v>
+      </c>
+      <c r="P167" s="6">
+        <v>0.034498</v>
       </c>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B168" s="7">
+      <c r="B168" s="6">
         <v>0.0974916</v>
       </c>
-      <c r="C168" s="7">
+      <c r="C168" s="6">
         <v>0.144942</v>
       </c>
-      <c r="D168" s="7">
+      <c r="D168" s="6">
         <v>0.14925</v>
       </c>
-      <c r="E168" s="7">
+      <c r="E168" s="6">
         <v>0.150428</v>
       </c>
-      <c r="F168" s="7">
+      <c r="F168" s="6">
         <v>0.123602</v>
       </c>
       <c r="G168" s="6">
@@ -9371,73 +9567,49 @@
       <c r="I168" s="4">
         <v>64</v>
       </c>
-      <c r="J168" s="7">
+      <c r="J168" s="6">
         <v>0.0347907</v>
       </c>
-      <c r="K168" s="7">
+      <c r="K168" s="6">
         <v>0.0328975</v>
       </c>
-      <c r="L168" s="7">
-        <v>0</v>
-      </c>
-      <c r="M168" s="7">
-        <v>0</v>
-      </c>
-      <c r="N168" s="7">
-        <v>0</v>
-      </c>
-      <c r="O168" s="7">
-        <v>0</v>
-      </c>
-      <c r="P168" s="7">
-        <v>0</v>
+      <c r="L168" s="6">
+        <v>0.032565</v>
+      </c>
+      <c r="M168" s="6">
+        <v>0.037764</v>
+      </c>
+      <c r="N168" s="6">
+        <v>0.032494</v>
+      </c>
+      <c r="O168" s="6">
+        <v>0.030268</v>
+      </c>
+      <c r="P168" s="6">
+        <v>0.032161</v>
       </c>
     </row>
     <row r="169" spans="1:16">
-      <c r="A169" s="8"/>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="F169" s="9"/>
-      <c r="G169" s="9"/>
-      <c r="H169" s="9"/>
-      <c r="I169" s="8"/>
-      <c r="J169" s="7"/>
-      <c r="K169" s="7"/>
-      <c r="L169" s="9"/>
-      <c r="M169" s="9"/>
-      <c r="N169" s="9"/>
-      <c r="O169" s="9"/>
-      <c r="P169" s="9"/>
+      <c r="A169" s="7"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8"/>
+      <c r="F169" s="8"/>
+      <c r="G169" s="8"/>
+      <c r="H169" s="8"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="6"/>
+      <c r="K169" s="6"/>
+      <c r="L169" s="8"/>
+      <c r="M169" s="8"/>
+      <c r="N169" s="8"/>
+      <c r="O169" s="8"/>
+      <c r="P169" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>